--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="327">
   <si>
     <t>FEATURE</t>
   </si>
@@ -21,7 +21,13 @@
     <t>STORY ID</t>
   </si>
   <si>
-    <t>TOTAL TESTS</t>
+    <t>TOTAL CASES</t>
+  </si>
+  <si>
+    <t>AUTOMATED</t>
+  </si>
+  <si>
+    <t>MANUAL</t>
   </si>
   <si>
     <t>PASSED</t>
@@ -30,9 +36,6 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
     <t>LAST RUN</t>
   </si>
   <si>
@@ -45,7 +48,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 13:00:29</t>
+    <t>2026-06-26 13:11:14</t>
   </si>
   <si>
     <t>PASS</t>
@@ -93,21 +96,21 @@
     <t>STATUS (PASS/FAIL)</t>
   </si>
   <si>
-    <t>Login-AC1-01</t>
-  </si>
-  <si>
-    <t>AC1: Visit site and try to login</t>
+    <t>Login-AC1-POS-01</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — POSITIVE</t>
   </si>
   <si>
     <t>Sign in with valid credentials and land on /select-location</t>
   </si>
   <si>
-    <t>Browser open at https://moontower.aiimone.com/Login; Email field and Sign In button visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to the login page
-2. Enter Email in the Email field
-3. Enter Password in the Password field
+    <t>Browser open at https://moontower.aiimone.com/Login; user account 'developers@moontower.com' exists; Email field, Password field and Sign In button are visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to https://moontower.aiimone.com/Login
+2. Enter 'developers@moontower.com' into the Email field
+3. Enter '12345678' into the Password field
 4. Click the 'Sign In' button</t>
   </si>
   <si>
@@ -115,94 +118,1006 @@
 Password: 12345678</t>
   </si>
   <si>
-    <t>Page redirects to /select-location; 'Select Your Location' heading is visible; 'Restaurant: &lt;name&gt;' paragraph confirms an account context was loaded</t>
-  </si>
-  <si>
-    <t>User is authenticated and on the location-picker screen</t>
-  </si>
-  <si>
-    <t>Passed in 4.1s on chromium.</t>
-  </si>
-  <si>
-    <t>SignUp-001-AC1-01</t>
-  </si>
-  <si>
-    <t>AC1: Fill the signup form and register as a new user</t>
-  </si>
-  <si>
-    <t>Submit step-1 + step-2 form data and confirm the server accepts the registration</t>
-  </si>
-  <si>
-    <t>Browser open at https://moontower.aiimone.com/signup; step-1 form 'Register Your Restaurant' is visible; Next button is enabled</t>
+    <t>Page redirects to /select-location; 'Select Your Location' heading is visible; 'Restaurant: &lt;name&gt;' paragraph confirms the account context</t>
+  </si>
+  <si>
+    <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
+  </si>
+  <si>
+    <t>Passed in 16.0s on chromium.</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-01</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (wrong password)</t>
+  </si>
+  <si>
+    <t>Sign in with a valid email but an incorrect password</t>
+  </si>
+  <si>
+    <t>Browser open at /Login; valid email 'developers@moontower.com' exists in the system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Enter 'developers@moontower.com' into the Email field
+3. Enter a deliberately wrong password (e.g., 'WrongPass!2025') into the Password field
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: developers@moontower.com
+Password: WrongPass!2025</t>
+  </si>
+  <si>
+    <t>User remains on /Login; an error message (e.g., 'Invalid credentials' / 'Incorrect email or password') is visible; no redirect occurs</t>
+  </si>
+  <si>
+    <t>User is NOT authenticated; no session cookie set</t>
+  </si>
+  <si>
+    <t>Manual test case — execute per the TEST STEPS column.</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-02</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (non-existent email)</t>
+  </si>
+  <si>
+    <t>Sign in with an email that doesn't exist in the system</t>
+  </si>
+  <si>
+    <t>Browser open at /Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Enter a fresh, unregistered email into the Email field
+3. Enter any password
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: not-a-real-user@example.com
+Password: AnyPass!123</t>
+  </si>
+  <si>
+    <t>User remains on /Login; an error message indicates invalid credentials (the system should NOT leak whether the email exists, to prevent account enumeration)</t>
+  </si>
+  <si>
+    <t>User is NOT authenticated</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-03</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (empty email)</t>
+  </si>
+  <si>
+    <t>Submit form with the Email field left empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Leave the Email field blank
+3. Enter a valid password
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: (empty)
+Password: 12345678</t>
+  </si>
+  <si>
+    <t>Sign In button is either disabled OR a validation message appears under the Email field ('Email is required'); no network request is made</t>
+  </si>
+  <si>
+    <t>User remains on /Login; no authentication attempt</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-04</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (empty password)</t>
+  </si>
+  <si>
+    <t>Submit form with the Password field left empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Enter a valid email
+3. Leave the Password field blank
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: developers@moontower.com
+Password: (empty)</t>
+  </si>
+  <si>
+    <t>Sign In button is either disabled OR a validation message appears under the Password field ('Password is required'); no network request is made</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-05</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (both fields empty)</t>
+  </si>
+  <si>
+    <t>Submit form with both Email and Password fields empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Leave both fields blank
+3. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: (empty)
+Password: (empty)</t>
+  </si>
+  <si>
+    <t>Sign In button is disabled OR validation messages appear under both fields; no network request is made</t>
+  </si>
+  <si>
+    <t>User remains on /Login</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-06</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (invalid email format)</t>
+  </si>
+  <si>
+    <t>Submit form with an email that doesn't contain '@'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Enter 'developersmoontower.com' (missing @) in Email
+3. Enter any password
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: developersmoontower.com
+Password: 12345678</t>
+  </si>
+  <si>
+    <t>Validation message appears: 'Please enter a valid email address' (HTML5 or app-level validation); form is not submitted</t>
+  </si>
+  <si>
+    <t>Login-AC1-NEG-07</t>
+  </si>
+  <si>
+    <t>Submit form with an email missing the domain part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Enter 'developers@' into the Email field
+3. Enter any password
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: developers@
+Password: 12345678</t>
+  </si>
+  <si>
+    <t>Validation message appears; form is not submitted</t>
+  </si>
+  <si>
+    <t>Login-UI-01</t>
+  </si>
+  <si>
+    <t>Login form UI behavior</t>
+  </si>
+  <si>
+    <t>Password field masks the input by default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Type any text into the Password field
+3. Inspect the input — characters should render as dots or asterisks</t>
+  </si>
+  <si>
+    <t>Password: TestPass123</t>
+  </si>
+  <si>
+    <t>Password field has type='password'; the typed text is rendered as masked characters (•••••••••••), not as plaintext</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Login-UI-02</t>
+  </si>
+  <si>
+    <t>'Show password' button reveals the password text</t>
+  </si>
+  <si>
+    <t>Browser open at /Login; password field has some text in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Type a password into the Password field
+3. Click the 'Show password' button (eye icon)</t>
+  </si>
+  <si>
+    <t>Password field's input type switches to 'text'; the typed characters are now visible in plaintext</t>
+  </si>
+  <si>
+    <t>n/a — the visibility toggle should be reversible</t>
+  </si>
+  <si>
+    <t>Login-UI-03</t>
+  </si>
+  <si>
+    <t>Pressing Enter inside the Password field submits the form</t>
+  </si>
+  <si>
+    <t>Browser open at /Login with valid credentials filled in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill Email with valid value
+2. Fill Password with valid value
+3. Press Enter key while focus is on the Password field</t>
+  </si>
+  <si>
+    <t>Form is submitted (equivalent to clicking Sign In); on success, user is redirected to /select-location</t>
+  </si>
+  <si>
+    <t>User is signed in</t>
+  </si>
+  <si>
+    <t>Login-UI-04</t>
+  </si>
+  <si>
+    <t>Login form keyboard accessibility</t>
+  </si>
+  <si>
+    <t>Tab order: Email → Password → 'Show password' → 'Forgot password?' → Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Click into the Email field (or press Tab from the address bar)
+3. Press Tab repeatedly and observe which element receives focus</t>
+  </si>
+  <si>
+    <t>Focus moves predictably through Email → Password → Show-password → Forgot link → Sign In; no element is skipped or unreachable via keyboard</t>
+  </si>
+  <si>
+    <t>Login-NAV-01</t>
+  </si>
+  <si>
+    <t>Login page navigation links</t>
+  </si>
+  <si>
+    <t>'Forgot password?' link navigates to /forgot-password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Click the 'Forgot password?' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to https://moontower.aiimone.com/forgot-password</t>
+  </si>
+  <si>
+    <t>User is on the forgot-password screen</t>
+  </si>
+  <si>
+    <t>Login-NAV-02</t>
+  </si>
+  <si>
+    <t>'Sign up' link navigates to /signup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Click the 'Sign up' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to https://moontower.aiimone.com/signup</t>
+  </si>
+  <si>
+    <t>User is on the signup screen</t>
+  </si>
+  <si>
+    <t>Login-NAV-03</t>
+  </si>
+  <si>
+    <t>'← Back' link navigates to the homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Click the '← Back' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to https://moontower.aiimone.com/ (homepage)</t>
+  </si>
+  <si>
+    <t>User is on the homepage</t>
+  </si>
+  <si>
+    <t>Login-EDGE-01</t>
+  </si>
+  <si>
+    <t>Login edge cases</t>
+  </si>
+  <si>
+    <t>Login with leading/trailing whitespace in the email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter '  developers@moontower.com  ' (with spaces) in Email
+2. Enter the valid password
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: '  developers@moontower.com  '
+Password: 12345678</t>
+  </si>
+  <si>
+    <t>App SHOULD trim whitespace and authenticate successfully — OR show a clear validation error. Either is acceptable; silent failure is not.</t>
+  </si>
+  <si>
+    <t>Login-EDGE-02</t>
+  </si>
+  <si>
+    <t>Login with email in uppercase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'DEVELOPERS@MOONTOWER.COM' in Email
+2. Enter the valid password
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: DEVELOPERS@MOONTOWER.COM
+Password: 12345678</t>
+  </si>
+  <si>
+    <t>App should authenticate successfully (email addresses are case-insensitive per RFC 5321 for the local part by convention, and case-insensitive for the domain part)</t>
+  </si>
+  <si>
+    <t>Login-EDGE-03</t>
+  </si>
+  <si>
+    <t>Login with very long email (256+ characters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Generate an email of 260 characters total (e.g., 250-char local part + '@x.co')
+2. Paste into Email field
+3. Enter any password and click Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: &lt;250 random chars&gt;@x.co
+Password: 12345678</t>
+  </si>
+  <si>
+    <t>Validation rejects the email as invalid (RFC 5321 limit is 254 chars total); no buffer overflow / 500 error</t>
+  </si>
+  <si>
+    <t>Login-SEC-01</t>
+  </si>
+  <si>
+    <t>Login security</t>
+  </si>
+  <si>
+    <t>Password input element has type='password' (not visible in DOM as plaintext)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
+2. Open DevTools → Elements
+3. Inspect the password input</t>
+  </si>
+  <si>
+    <t>The input has the attribute type='password'; the typed value is masked in the visible DOM</t>
+  </si>
+  <si>
+    <t>Login-SEC-02</t>
+  </si>
+  <si>
+    <t>Credentials are not appended to the URL after submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill valid credentials and click Sign In
+2. Inspect the address bar after submission and during the redirect</t>
+  </si>
+  <si>
+    <t>URL never contains email or password as query parameters (form must POST, not GET); no credential traces in browser history</t>
+  </si>
+  <si>
+    <t>Credentials not exposed via URL</t>
+  </si>
+  <si>
+    <t>Login-SEC-03</t>
+  </si>
+  <si>
+    <t>SQL-injection-style payload in Email field is handled safely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter "admin' OR '1'='1" in the Email field
+2. Enter any password
+3. Click Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: admin' OR '1'='1
+Password: anything</t>
+  </si>
+  <si>
+    <t>The app treats the input as a normal string; either the email-format validator rejects it OR the backend rejects with 'Invalid credentials'. No DB error surfaces; no successful login.</t>
+  </si>
+  <si>
+    <t>User remains on /Login; no DB compromise</t>
+  </si>
+  <si>
+    <t>Login-SEC-04</t>
+  </si>
+  <si>
+    <t>Rate limiting / account lockout after multiple failed attempts</t>
+  </si>
+  <si>
+    <t>Browser open at /Login; valid email known</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Submit wrong-password attempt for the same email N times in quick succession (e.g., 5–10 times)
+2. Observe whether subsequent attempts are throttled or locked out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: developers@moontower.com
+Password: wrong-password-attempts</t>
+  </si>
+  <si>
+    <t>After a threshold of failed attempts, the system either rate-limits the next attempt (HTTP 429 / 'Too many attempts, try again later') or locks the account temporarily. Indefinite unlimited attempts are a security gap.</t>
+  </si>
+  <si>
+    <t>Account is throttled or locked; legitimate user notified via email (ideally)</t>
+  </si>
+  <si>
+    <t>SignUp-001-AC1-POS-01</t>
+  </si>
+  <si>
+    <t>AC1: Fill signup form and register — POSITIVE (happy path)</t>
+  </si>
+  <si>
+    <t>Complete the 2-step signup with valid data; server accepts the registration</t>
+  </si>
+  <si>
+    <t>Browser open at /signup; step-1 'Register Your Restaurant' form is visible</t>
   </si>
   <si>
     <t xml:space="preserve">1. Fill Restaurant Name with a unique timestamp-suffixed value
 2. Verify Subdomain auto-populates (read-only)
-3. Fill Full Name, Business Email, Phone Number
-4. Click 'Next' to advance to step 2
-5. Fill Password and Confirm Password
+3. Fill Full Name, Business Email, Phone Number with valid values
+4. Click 'Next' → step-2 'Set Password' appears
+5. Fill Password and Confirm Password (matching)
 6. Check 'I agree to the Terms and Conditions'
 7. Click 'Create Account'</t>
   </si>
   <si>
-    <t xml:space="preserve">Restaurant Name: MoonTest&lt;timestamp&gt;
+    <t xml:space="preserve">Restaurant: MoonTest&lt;ts&gt;
 Full Name: Arslan Tester
-Email: arslan.moon+ac1&lt;timestamp&gt;@yopmail.com
+Email: arslan.moon+ac1&lt;ts&gt;@yopmail.com
 Phone: 5555550199
 Password: TestPass!2025</t>
   </si>
   <si>
-    <t>Form is accepted; URL leaves /signup (no validation errors); the app navigates the user away from the signup screen</t>
-  </si>
-  <si>
-    <t>A new restaurant tenant exists on the server with the unique restaurant name; the user is on the post-signup flow</t>
-  </si>
-  <si>
-    <t>Passed in 4.5s on chromium.</t>
-  </si>
-  <si>
-    <t>SignUp-001-AC2-01</t>
-  </si>
-  <si>
-    <t>AC2: Verify the user is registered</t>
-  </si>
-  <si>
-    <t>After Create Account, confirm three independent post-registration signals all hold</t>
-  </si>
-  <si>
-    <t>Browser open at https://moontower.aiimone.com/signup; step-1 form visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all step-1 required fields with valid data
-2. Click 'Next' to reach step 2
-3. Fill passwords and accept Terms
-4. Click 'Create Account'
-5. Verify the URL is /select-location
-6. Verify 'Select Your Location' heading is visible
-7. Verify the 'Restaurant: &lt;run-specific name&gt;' paragraph is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant Name: MoonVerify&lt;timestamp&gt;
-Full Name: Arslan Verify
-Email: arslan.moon+ac2&lt;timestamp&gt;@yopmail.com
-Phone: 5555550199
+    <t>Server accepts registration; URL leaves /signup (typically navigates to /select-location)</t>
+  </si>
+  <si>
+    <t>New tenant created on server; user can proceed to choose a location</t>
+  </si>
+  <si>
+    <t>Passed in 16.1s on chromium.</t>
+  </si>
+  <si>
+    <t>SignUp-001-AC2-POS-01</t>
+  </si>
+  <si>
+    <t>AC2: Verify the user is registered — POSITIVE</t>
+  </si>
+  <si>
+    <t>After Create Account, three independent post-registration signals all hold</t>
+  </si>
+  <si>
+    <t>Browser open at /signup; valid registration just submitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete the full 2-step signup with valid data
+2. Verify the URL equals /select-location
+3. Verify the 'Select Your Location' heading is visible
+4. Verify the 'Restaurant: &lt;name&gt;' paragraph references the just-created restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant: MoonVerify&lt;ts&gt;
+Email: arslan.moon+ac2&lt;ts&gt;@yopmail.com
 Password: TestPass!2025</t>
   </si>
   <si>
-    <t>All three signals hold simultaneously: URL = /select-location; 'Select Your Location' heading visible; 'Restaurant: &lt;run-specific name&gt;' paragraph confirms the exact account just created</t>
-  </si>
-  <si>
-    <t>Registration is confirmed end-to-end; user can now choose a location to manage</t>
-  </si>
-  <si>
-    <t>Passed in 4.4s on chromium.</t>
+    <t>All three signals visible simultaneously: URL = /select-location, heading visible, restaurant paragraph confirms the new account</t>
+  </si>
+  <si>
+    <t>Registration confirmed end-to-end</t>
+  </si>
+  <si>
+    <t>Passed in 16.2s on chromium.</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-01</t>
+  </si>
+  <si>
+    <t>Step 1 validation — required field missing</t>
+  </si>
+  <si>
+    <t>Submit step 1 with Restaurant Name empty</t>
+  </si>
+  <si>
+    <t>Browser open at /signup; step-1 form visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave Restaurant Name empty
+2. Fill all other required step-1 fields with valid values
+3. Click 'Next'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant Name: (empty)
+Full Name: Arslan
+Email: arslan.moon+rn@yopmail.com
+Phone: 5555550199</t>
+  </si>
+  <si>
+    <t>'Next' is disabled OR a validation message appears under Restaurant Name; form does not advance to step 2</t>
+  </si>
+  <si>
+    <t>User remains on step 1</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-02</t>
+  </si>
+  <si>
+    <t>Submit step 1 with Full Name empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill Restaurant Name; leave Full Name empty
+2. Fill remaining required fields
+3. Click 'Next'</t>
+  </si>
+  <si>
+    <t>Full Name: (empty)</t>
+  </si>
+  <si>
+    <t>Validation message appears; form does not advance</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-03</t>
+  </si>
+  <si>
+    <t>Submit step 1 with Business Email empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all step-1 fields except Business Email
+2. Click 'Next'</t>
+  </si>
+  <si>
+    <t>Business Email: (empty)</t>
+  </si>
+  <si>
+    <t>Validation message appears under Business Email; form does not advance</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-04</t>
+  </si>
+  <si>
+    <t>Step 1 validation — invalid email format</t>
+  </si>
+  <si>
+    <t>Submit step 1 with a Business Email that has no '@' symbol</t>
+  </si>
+  <si>
+    <t>Browser open at /signup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all step-1 fields
+2. In Business Email enter 'arslan.moon-yopmail.com' (no @)
+3. Click 'Next'</t>
+  </si>
+  <si>
+    <t>Business Email: arslan.moon-yopmail.com</t>
+  </si>
+  <si>
+    <t>Validation message: 'Please enter a valid email address'; form does not advance</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-05</t>
+  </si>
+  <si>
+    <t>Step 1 validation — invalid phone format</t>
+  </si>
+  <si>
+    <t>Submit step 1 with letters in the Phone Number field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all step-1 fields
+2. In Phone Number enter 'abc1234567'
+3. Click 'Next'</t>
+  </si>
+  <si>
+    <t>Phone Number: abc1234567</t>
+  </si>
+  <si>
+    <t>Validation message rejects the input OR the field strips non-digits; form does not advance if invalid</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-06</t>
+  </si>
+  <si>
+    <t>Step 1 — email uniqueness (server-side)</t>
+  </si>
+  <si>
+    <t>Submit step 1 with an email already registered in the system</t>
+  </si>
+  <si>
+    <t>An account already exists for 'arslan.moon@yopmail.com'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all step-1 fields, using the already-registered email
+2. Click 'Next' (step 2 may appear depending on when the uniqueness check fires)
+3. Complete step 2 if reached and click 'Create Account'</t>
+  </si>
+  <si>
+    <t>Business Email: arslan.moon@yopmail.com</t>
+  </si>
+  <si>
+    <t>Server rejects with a message such as 'Email already in use'; URL stays on /signup; no new tenant created</t>
+  </si>
+  <si>
+    <t>No duplicate account; existing account untouched</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-07</t>
+  </si>
+  <si>
+    <t>Step 1 — Subdomain auto-population</t>
+  </si>
+  <si>
+    <t>Subdomain is read-only and auto-derived from Restaurant Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Inspect the Subdomain input; confirm it has the readonly attribute
+2. Type a Restaurant Name (e.g., 'My Eatery 42')
+3. Observe the Subdomain field</t>
+  </si>
+  <si>
+    <t>Restaurant Name: My Eatery 42</t>
+  </si>
+  <si>
+    <t>Subdomain becomes 'myeatery42' (lowercased, alphanumeric only); user cannot edit it directly</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-08</t>
+  </si>
+  <si>
+    <t>Step 2 — password validation (mismatch)</t>
+  </si>
+  <si>
+    <t>Step 2 rejects mismatching Password and Confirm Password values</t>
+  </si>
+  <si>
+    <t>Step 2 'Set Password' is visible (step 1 completed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'TestPass!2025' in Password
+2. Enter 'DifferentPass!2025' in Confirm Password
+3. Check the Terms checkbox
+4. Attempt to click 'Create Account'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password: TestPass!2025
+Confirm Password: DifferentPass!2025</t>
+  </si>
+  <si>
+    <t>Validation message: 'Passwords do not match'; Create Account is disabled OR submission is blocked</t>
+  </si>
+  <si>
+    <t>User remains on step 2</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-09</t>
+  </si>
+  <si>
+    <t>Step 2 — password validation (too short)</t>
+  </si>
+  <si>
+    <t>Step 2 enforces a minimum password length</t>
+  </si>
+  <si>
+    <t>Step 2 visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a short password (e.g., 'abc') in both Password and Confirm Password
+2. Check Terms
+3. Attempt Create Account</t>
+  </si>
+  <si>
+    <t>Password: abc</t>
+  </si>
+  <si>
+    <t>Validation message: minimum-length requirement is not met; submission is blocked</t>
+  </si>
+  <si>
+    <t>SignUp-001-NEG-10</t>
+  </si>
+  <si>
+    <t>Step 2 — terms checkbox required</t>
+  </si>
+  <si>
+    <t>Create Account is disabled until 'I agree to the Terms and Conditions' is checked</t>
+  </si>
+  <si>
+    <t>Step 2 visible; passwords filled with matching valid values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill Password and Confirm Password with valid matching values
+2. Leave the Terms checkbox UNCHECKED
+3. Observe the Create Account button state</t>
+  </si>
+  <si>
+    <t>Terms checkbox: unchecked</t>
+  </si>
+  <si>
+    <t>Create Account button is disabled; cannot be clicked</t>
+  </si>
+  <si>
+    <t>SignUp-001-UI-01</t>
+  </si>
+  <si>
+    <t>Step 1 — read-only fields</t>
+  </si>
+  <si>
+    <t>Subdomain, Location Name, and Address fields are read-only and cannot be edited by clicking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open DevTools → Elements
+2. Confirm each of #subDomain, #locationName, #locationAddress has the readonly attribute
+3. Click into each and attempt to type</t>
+  </si>
+  <si>
+    <t>None of the three fields accept keyboard input; the readonly attribute is set on the input elements</t>
+  </si>
+  <si>
+    <t>SignUp-001-UI-02</t>
+  </si>
+  <si>
+    <t>Step 1/2 — Next button gating</t>
+  </si>
+  <si>
+    <t>Next button reflects validity of step-1 required fields in real time</t>
+  </si>
+  <si>
+    <t>Browser open at /signup; form is empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Observe the Next button state when the form is empty
+2. Progressively fill each required field
+3. Observe the Next button state at each step</t>
+  </si>
+  <si>
+    <t>Next button is disabled when any required field is empty/invalid; becomes enabled once all required fields have valid values</t>
+  </si>
+  <si>
+    <t>SignUp-001-UI-03</t>
+  </si>
+  <si>
+    <t>Step 2 — password visibility toggle</t>
+  </si>
+  <si>
+    <t>Both Password and Confirm Password fields have a working show/hide toggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Type into Password
+2. Click the 'Show password' button next to Password
+3. Click again to re-mask
+4. Repeat for Confirm Password</t>
+  </si>
+  <si>
+    <t>Password: TestPass!2025</t>
+  </si>
+  <si>
+    <t>Each show-password button toggles the corresponding field between type='password' and type='text'; mask state is independent for the two fields</t>
+  </si>
+  <si>
+    <t>SignUp-001-UI-04</t>
+  </si>
+  <si>
+    <t>Step 2 — Back button preserves step-1 data</t>
+  </si>
+  <si>
+    <t>Clicking Back from step 2 returns to step 1 with the previously entered values intact</t>
+  </si>
+  <si>
+    <t>Step 1 was filled and Next clicked; user is on step 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On step 2, click 'Back'
+2. Inspect each step-1 field</t>
+  </si>
+  <si>
+    <t>Step 1 reappears; all editable fields retain the values entered previously (no data loss)</t>
+  </si>
+  <si>
+    <t>User can navigate back and forth between steps without losing input</t>
+  </si>
+  <si>
+    <t>SignUp-001-NAV-01</t>
+  </si>
+  <si>
+    <t>Signup page navigation</t>
+  </si>
+  <si>
+    <t>'Sign in' link on /signup navigates to /login</t>
+  </si>
+  <si>
+    <t>1. Click the 'Sign in' link below the form</t>
+  </si>
+  <si>
+    <t>Browser navigates to /login</t>
+  </si>
+  <si>
+    <t>User on the login screen</t>
+  </si>
+  <si>
+    <t>SignUp-001-NAV-02</t>
+  </si>
+  <si>
+    <t>'← Back' link navigates to /</t>
+  </si>
+  <si>
+    <t>1. Click the '← Back' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to the homepage</t>
+  </si>
+  <si>
+    <t>User on the homepage</t>
+  </si>
+  <si>
+    <t>SignUp-001-EDGE-01</t>
+  </si>
+  <si>
+    <t>Signup edge cases</t>
+  </si>
+  <si>
+    <t>Restaurant Name with leading/trailing whitespace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter '   My Eatery   ' in Restaurant Name
+2. Observe the Subdomain auto-fill
+3. Complete the rest of step 1 and proceed</t>
+  </si>
+  <si>
+    <t>Restaurant Name: '   My Eatery   '</t>
+  </si>
+  <si>
+    <t>App trims whitespace before deriving the subdomain; subdomain is 'myeatery' not 'my-eatery'</t>
+  </si>
+  <si>
+    <t>SignUp-001-EDGE-02</t>
+  </si>
+  <si>
+    <t>Restaurant Name with special characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'My Eatery &amp; Café (2026)!' in Restaurant Name
+2. Observe Subdomain auto-fill</t>
+  </si>
+  <si>
+    <t>Restaurant Name: My Eatery &amp; Café (2026)!</t>
+  </si>
+  <si>
+    <t>Subdomain is derived to a URL-safe slug (alphanumeric + dashes only): e.g., 'myeaterycafe2026'; no special characters leak into the subdomain</t>
+  </si>
+  <si>
+    <t>SignUp-001-EDGE-03</t>
+  </si>
+  <si>
+    <t>Disposable email (yopmail) is accepted (or rejected with clear message)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use a yopmail address (e.g., arslan.moon+test@yopmail.com)
+2. Complete signup</t>
+  </si>
+  <si>
+    <t>Email: arslan.moon+test&lt;ts&gt;@yopmail.com</t>
+  </si>
+  <si>
+    <t>App either (a) accepts the email and proceeds with signup, or (b) explicitly rejects with 'Disposable email addresses are not allowed'. Silent failure is not acceptable.</t>
+  </si>
+  <si>
+    <t>SignUp-001-EDGE-04</t>
+  </si>
+  <si>
+    <t>Subdomain collision — Restaurant Name yields a subdomain that already exists</t>
+  </si>
+  <si>
+    <t>An account 'demo' already exists; new user tries Restaurant Name 'Demo'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'Demo' as Restaurant Name (auto-derives to existing subdomain 'demo')
+2. Complete the full form and click Create Account</t>
+  </si>
+  <si>
+    <t>Restaurant Name: Demo (collides with existing tenant)</t>
+  </si>
+  <si>
+    <t>Server rejects the registration with a clear message: 'Subdomain already in use' or similar; URL stays on /signup</t>
+  </si>
+  <si>
+    <t>No duplicate tenant created</t>
+  </si>
+  <si>
+    <t>SignUp-001-SEC-01</t>
+  </si>
+  <si>
+    <t>Signup security</t>
+  </si>
+  <si>
+    <t>Password fields use type='password' (masked, not in DOM as plaintext)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Inspect both Password and Confirm Password inputs in DevTools
+2. Confirm their initial type attribute</t>
+  </si>
+  <si>
+    <t>Both inputs default to type='password'; values are masked in the DOM by default</t>
+  </si>
+  <si>
+    <t>SignUp-001-SEC-02</t>
+  </si>
+  <si>
+    <t>Form posts over HTTPS (credentials encrypted in transit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open DevTools → Network
+2. Submit the form
+3. Inspect the request URL and protocol</t>
+  </si>
+  <si>
+    <t>The form-submit request goes to an https:// endpoint; no plaintext HTTP credentials in transit</t>
+  </si>
+  <si>
+    <t>SignUp-001-SEC-03</t>
+  </si>
+  <si>
+    <t>XSS payload in Restaurant Name is sanitized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter '&lt;script&gt;alert(1)&lt;/script&gt;' as Restaurant Name
+2. Complete signup and observe the post-signup screen 'Restaurant: &lt;name&gt;' paragraph</t>
+  </si>
+  <si>
+    <t>Restaurant Name: &lt;script&gt;alert(1)&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>No JS alert fires; the value is either rejected at input validation OR rendered as escaped text (no HTML injection)</t>
+  </si>
+  <si>
+    <t>n/a — XSS does not execute</t>
+  </si>
+  <si>
+    <t>SignUp-001-SEC-04</t>
+  </si>
+  <si>
+    <t>Password not echoed in the response or DOM after successful submission</t>
+  </si>
+  <si>
+    <t>Successful signup just completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. After Create Account succeeds, open DevTools
+2. Search the DOM for the password string
+3. Inspect the network response for any password field</t>
+  </si>
+  <si>
+    <t>Password string does NOT appear anywhere in the DOM or in any HTTP response body. (Only the hashed/transient form submission contained it.)</t>
+  </si>
+  <si>
+    <t>Password not leaked</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -231,8 +1146,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF4338CA"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,6 +1173,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -282,7 +1208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -295,6 +1221,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,18 +1564,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,83 +1600,95 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2">
+        <v>24</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -775,66 +1716,738 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>11</v>
+      <c r="G12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +2458,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -862,98 +2475,866 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" ht="98" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>42</v>
+        <v>170</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="98" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>52</v>
+        <v>180</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="338">
   <si>
     <t>FEATURE</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 13:11:14</t>
+    <t>2026-06-26 13:23:58</t>
   </si>
   <si>
     <t>PASS</t>
@@ -124,7 +124,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>Passed in 16.0s on chromium.</t>
+    <t>Passed in 4.5s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -146,16 +146,16 @@
   </si>
   <si>
     <t xml:space="preserve">Email: developers@moontower.com
-Password: WrongPass!2025</t>
-  </si>
-  <si>
-    <t>User remains on /Login; an error message (e.g., 'Invalid credentials' / 'Incorrect email or password') is visible; no redirect occurs</t>
+Password: WrongPassword!2025</t>
+  </si>
+  <si>
+    <t>Auth API returns non-2xx (401); URL stays on /login; no redirect to /select-location</t>
   </si>
   <si>
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
-    <t>Manual test case — execute per the TEST STEPS column.</t>
+    <t>Passed in 4.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -171,19 +171,22 @@
   </si>
   <si>
     <t xml:space="preserve">1. Navigate to /Login
-2. Enter a fresh, unregistered email into the Email field
+2. Enter a fresh, unregistered email (e.g., no-such-user-&lt;timestamp&gt;@example.com)
 3. Enter any password
 4. Click 'Sign In'</t>
   </si>
   <si>
-    <t xml:space="preserve">Email: not-a-real-user@example.com
-Password: AnyPass!123</t>
-  </si>
-  <si>
-    <t>User remains on /Login; an error message indicates invalid credentials (the system should NOT leak whether the email exists, to prevent account enumeration)</t>
+    <t xml:space="preserve">Email: no-such-user-&lt;timestamp&gt;@example.com
+Password: AnyPass!1234</t>
+  </si>
+  <si>
+    <t>Auth API returns non-2xx; URL stays on /login</t>
   </si>
   <si>
     <t>User is NOT authenticated</t>
+  </si>
+  <si>
+    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -197,18 +200,21 @@
   <si>
     <t xml:space="preserve">1. Navigate to /Login
 2. Leave the Email field blank
-3. Enter a valid password
+3. Enter a password
 4. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: (empty)
-Password: 12345678</t>
-  </si>
-  <si>
-    <t>Sign In button is either disabled OR a validation message appears under the Email field ('Email is required'); no network request is made</t>
-  </si>
-  <si>
-    <t>User remains on /Login; no authentication attempt</t>
+Password: Whatever!2025</t>
+  </si>
+  <si>
+    <t>Form does not navigate to /select-location; user remains on /Login</t>
+  </si>
+  <si>
+    <t>User remains on /Login; no authentication</t>
+  </si>
+  <si>
+    <t>Passed in 5.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -230,7 +236,10 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Sign In button is either disabled OR a validation message appears under the Password field ('Password is required'); no network request is made</t>
+    <t>User remains on /Login</t>
+  </si>
+  <si>
+    <t>Passed in 8.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-05</t>
@@ -251,16 +260,13 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Sign In button is disabled OR validation messages appear under both fields; no network request is made</t>
-  </si>
-  <si>
-    <t>User remains on /Login</t>
+    <t>Passed in 5.6s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (invalid email format)</t>
+    <t>AC1: Visit site and try to login — NEGATIVE (invalid email format, no @)</t>
   </si>
   <si>
     <t>Submit form with an email that doesn't contain '@'</t>
@@ -273,13 +279,19 @@
   </si>
   <si>
     <t xml:space="preserve">Email: developersmoontower.com
-Password: 12345678</t>
-  </si>
-  <si>
-    <t>Validation message appears: 'Please enter a valid email address' (HTML5 or app-level validation); form is not submitted</t>
+Password: Whatever!2025</t>
+  </si>
+  <si>
+    <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
+  </si>
+  <si>
+    <t>Passed in 4.2s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
+  </si>
+  <si>
+    <t>AC1: Visit site and try to login — NEGATIVE (invalid email format, missing domain)</t>
   </si>
   <si>
     <t>Submit form with an email missing the domain part</t>
@@ -292,10 +304,10 @@
   </si>
   <si>
     <t xml:space="preserve">Email: developers@
-Password: 12345678</t>
-  </si>
-  <si>
-    <t>Validation message appears; form is not submitted</t>
+Password: Whatever!2025</t>
+  </si>
+  <si>
+    <t>Passed in 4.8s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-01</t>
@@ -304,47 +316,49 @@
     <t>Login form UI behavior</t>
   </si>
   <si>
-    <t>Password field masks the input by default</t>
+    <t>Password field masks the input by default (type='password')</t>
   </si>
   <si>
     <t xml:space="preserve">1. Navigate to /Login
-2. Type any text into the Password field
-3. Inspect the input — characters should render as dots or asterisks</t>
-  </si>
-  <si>
-    <t>Password: TestPass123</t>
-  </si>
-  <si>
-    <t>Password field has type='password'; the typed text is rendered as masked characters (•••••••••••), not as plaintext</t>
+2. Inspect the Password input element</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
+    <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
+  </si>
+  <si>
+    <t>Passed in 3.2s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-02</t>
   </si>
   <si>
-    <t>'Show password' button reveals the password text</t>
-  </si>
-  <si>
-    <t>Browser open at /Login; password field has some text in it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Type a password into the Password field
-3. Click the 'Show password' button (eye icon)</t>
-  </si>
-  <si>
-    <t>Password field's input type switches to 'text'; the typed characters are now visible in plaintext</t>
-  </si>
-  <si>
-    <t>n/a — the visibility toggle should be reversible</t>
+    <t>'Show password' button toggles input type between password and text</t>
+  </si>
+  <si>
+    <t>Browser open at /Login; password field has text in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Type a password into the Password field
+2. Click the 'Show password' button (eye icon)
+3. Click again to re-mask</t>
+  </si>
+  <si>
+    <t>Password: Secret!2025</t>
+  </si>
+  <si>
+    <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
+  </si>
+  <si>
+    <t>Passed in 4.7s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-03</t>
   </si>
   <si>
-    <t>Pressing Enter inside the Password field submits the form</t>
+    <t>Pressing Enter inside the Password field submits the form (equivalent to clicking Sign In)</t>
   </si>
   <si>
     <t>Browser open at /Login with valid credentials filled in</t>
@@ -355,10 +369,13 @@
 3. Press Enter key while focus is on the Password field</t>
   </si>
   <si>
-    <t>Form is submitted (equivalent to clicking Sign In); on success, user is redirected to /select-location</t>
+    <t>Form submits; on success, user is redirected to /select-location</t>
   </si>
   <si>
     <t>User is signed in</t>
+  </si>
+  <si>
+    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-04</t>
@@ -378,6 +395,9 @@
     <t>Focus moves predictably through Email → Password → Show-password → Forgot link → Sign In; no element is skipped or unreachable via keyboard</t>
   </si>
   <si>
+    <t>Manual test case — execute per the TEST STEPS column.</t>
+  </si>
+  <si>
     <t>Login-NAV-01</t>
   </si>
   <si>
@@ -391,10 +411,13 @@
 2. Click the 'Forgot password?' link</t>
   </si>
   <si>
-    <t>Browser navigates to https://moontower.aiimone.com/forgot-password</t>
-  </si>
-  <si>
-    <t>User is on the forgot-password screen</t>
+    <t>Link's href is '/forgot-password'; browser navigates to https://moontower.aiimone.com/forgot-password</t>
+  </si>
+  <si>
+    <t>User on the forgot-password screen</t>
+  </si>
+  <si>
+    <t>Passed in 3.5s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -407,10 +430,13 @@
 2. Click the 'Sign up' link</t>
   </si>
   <si>
-    <t>Browser navigates to https://moontower.aiimone.com/signup</t>
-  </si>
-  <si>
-    <t>User is on the signup screen</t>
+    <t>Link's href is '/signup'; browser navigates to https://moontower.aiimone.com/signup</t>
+  </si>
+  <si>
+    <t>User on the signup screen</t>
+  </si>
+  <si>
+    <t>Passed in 3.0s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -423,10 +449,10 @@
 2. Click the '← Back' link</t>
   </si>
   <si>
-    <t>Browser navigates to https://moontower.aiimone.com/ (homepage)</t>
-  </si>
-  <si>
-    <t>User is on the homepage</t>
+    <t>Link's href is '/'; browser navigates to the homepage</t>
+  </si>
+  <si>
+    <t>User on the homepage</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -465,7 +491,7 @@
 Password: 12345678</t>
   </si>
   <si>
-    <t>App should authenticate successfully (email addresses are case-insensitive per RFC 5321 for the local part by convention, and case-insensitive for the domain part)</t>
+    <t>App should authenticate successfully (email addresses are case-insensitive)</t>
   </si>
   <si>
     <t>Login-EDGE-03</t>
@@ -474,7 +500,7 @@
     <t>Login with very long email (256+ characters)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Generate an email of 260 characters total (e.g., 250-char local part + '@x.co')
+    <t xml:space="preserve">1. Generate an email of 260 characters total
 2. Paste into Email field
 3. Enter any password and click Sign In</t>
   </si>
@@ -483,7 +509,7 @@
 Password: 12345678</t>
   </si>
   <si>
-    <t>Validation rejects the email as invalid (RFC 5321 limit is 254 chars total); no buffer overflow / 500 error</t>
+    <t>Validation rejects the email as invalid (RFC 5321 limit is 254 chars total); no 500 error</t>
   </si>
   <si>
     <t>Login-SEC-01</t>
@@ -534,7 +560,7 @@
 Password: anything</t>
   </si>
   <si>
-    <t>The app treats the input as a normal string; either the email-format validator rejects it OR the backend rejects with 'Invalid credentials'. No DB error surfaces; no successful login.</t>
+    <t>The app treats the input as a string; either email validator rejects it OR auth API rejects with 'Invalid credentials'. No DB error surfaces; no successful login.</t>
   </si>
   <si>
     <t>User remains on /Login; no DB compromise</t>
@@ -554,13 +580,13 @@
   </si>
   <si>
     <t xml:space="preserve">Email: developers@moontower.com
-Password: wrong-password-attempts</t>
-  </si>
-  <si>
-    <t>After a threshold of failed attempts, the system either rate-limits the next attempt (HTTP 429 / 'Too many attempts, try again later') or locks the account temporarily. Indefinite unlimited attempts are a security gap.</t>
-  </si>
-  <si>
-    <t>Account is throttled or locked; legitimate user notified via email (ideally)</t>
+Password: &lt;wrong password attempts&gt;</t>
+  </si>
+  <si>
+    <t>After a threshold of failed attempts, the system rate-limits (HTTP 429) or locks the account temporarily. Indefinite unlimited attempts are a security gap.</t>
+  </si>
+  <si>
+    <t>Account is throttled or locked</t>
   </si>
   <si>
     <t>SignUp-001-AC1-POS-01</t>
@@ -585,19 +611,17 @@
   </si>
   <si>
     <t xml:space="preserve">Restaurant: MoonTest&lt;ts&gt;
-Full Name: Arslan Tester
 Email: arslan.moon+ac1&lt;ts&gt;@yopmail.com
-Phone: 5555550199
 Password: TestPass!2025</t>
   </si>
   <si>
-    <t>Server accepts registration; URL leaves /signup (typically navigates to /select-location)</t>
-  </si>
-  <si>
-    <t>New tenant created on server; user can proceed to choose a location</t>
-  </si>
-  <si>
-    <t>Passed in 16.1s on chromium.</t>
+    <t>Server accepts registration; URL leaves /signup</t>
+  </si>
+  <si>
+    <t>New tenant created; user proceeds to /select-location</t>
+  </si>
+  <si>
+    <t>Passed in 6.3s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-AC2-POS-01</t>
@@ -613,9 +637,9 @@
   </si>
   <si>
     <t xml:space="preserve">1. Complete the full 2-step signup with valid data
-2. Verify the URL equals /select-location
-3. Verify the 'Select Your Location' heading is visible
-4. Verify the 'Restaurant: &lt;name&gt;' paragraph references the just-created restaurant</t>
+2. Verify URL equals /select-location
+3. Verify 'Select Your Location' heading is visible
+4. Verify 'Restaurant: &lt;name&gt;' paragraph references the just-created restaurant</t>
   </si>
   <si>
     <t xml:space="preserve">Restaurant: MoonVerify&lt;ts&gt;
@@ -623,13 +647,13 @@
 Password: TestPass!2025</t>
   </si>
   <si>
-    <t>All three signals visible simultaneously: URL = /select-location, heading visible, restaurant paragraph confirms the new account</t>
+    <t>All three signals visible simultaneously</t>
   </si>
   <si>
     <t>Registration confirmed end-to-end</t>
   </si>
   <si>
-    <t>Passed in 16.2s on chromium.</t>
+    <t>Passed in 4.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-01</t>
@@ -650,12 +674,10 @@
   </si>
   <si>
     <t xml:space="preserve">Restaurant Name: (empty)
-Full Name: Arslan
-Email: arslan.moon+rn@yopmail.com
-Phone: 5555550199</t>
-  </si>
-  <si>
-    <t>'Next' is disabled OR a validation message appears under Restaurant Name; form does not advance to step 2</t>
+Email: arslan.moon+rn&lt;ts&gt;@yopmail.com</t>
+  </si>
+  <si>
+    <t>Form does not advance; step-1 heading 'Register Your Restaurant' still visible; step-2 heading 'Set Password' is NOT visible</t>
   </si>
   <si>
     <t>User remains on step 1</t>
@@ -675,7 +697,7 @@
     <t>Full Name: (empty)</t>
   </si>
   <si>
-    <t>Validation message appears; form does not advance</t>
+    <t>Form does not advance; step-1 heading still visible</t>
   </si>
   <si>
     <t>SignUp-001-NEG-03</t>
@@ -691,9 +713,6 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
-    <t>Validation message appears under Business Email; form does not advance</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
@@ -707,14 +726,14 @@
   </si>
   <si>
     <t xml:space="preserve">1. Fill all step-1 fields
-2. In Business Email enter 'arslan.moon-yopmail.com' (no @)
+2. In Business Email enter 'arslan-yopmail.com' (no @)
 3. Click 'Next'</t>
   </si>
   <si>
-    <t>Business Email: arslan.moon-yopmail.com</t>
-  </si>
-  <si>
-    <t>Validation message: 'Please enter a valid email address'; form does not advance</t>
+    <t>Business Email: arslan-yopmail.com</t>
+  </si>
+  <si>
+    <t>input[type=email] reports typeMismatch validity; form does not advance</t>
   </si>
   <si>
     <t>SignUp-001-NEG-05</t>
@@ -749,18 +768,18 @@
     <t>An account already exists for 'arslan.moon@yopmail.com'</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Fill all step-1 fields, using the already-registered email
-2. Click 'Next' (step 2 may appear depending on when the uniqueness check fires)
-3. Complete step 2 if reached and click 'Create Account'</t>
+    <t xml:space="preserve">1. Fill all step-1 fields using the already-registered email
+2. Click Next (may reach step 2)
+3. Complete step 2 if reached and click Create Account</t>
   </si>
   <si>
     <t>Business Email: arslan.moon@yopmail.com</t>
   </si>
   <si>
-    <t>Server rejects with a message such as 'Email already in use'; URL stays on /signup; no new tenant created</t>
-  </si>
-  <si>
-    <t>No duplicate account; existing account untouched</t>
+    <t>Server rejects with 'Email already in use' or similar; URL stays on /signup; no new tenant created</t>
+  </si>
+  <si>
+    <t>No duplicate account</t>
   </si>
   <si>
     <t>SignUp-001-NEG-07</t>
@@ -769,18 +788,18 @@
     <t>Step 1 — Subdomain auto-population</t>
   </si>
   <si>
-    <t>Subdomain is read-only and auto-derived from Restaurant Name</t>
+    <t>Subdomain is read-only and auto-derived from Restaurant Name (lowercased, kebab-cased)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Inspect the Subdomain input; confirm it has the readonly attribute
-2. Type a Restaurant Name (e.g., 'My Eatery 42')
-3. Observe the Subdomain field</t>
+2. Type 'My Eatery 42' into Restaurant Name
+3. Read the Subdomain value</t>
   </si>
   <si>
     <t>Restaurant Name: My Eatery 42</t>
   </si>
   <si>
-    <t>Subdomain becomes 'myeatery42' (lowercased, alphanumeric only); user cannot edit it directly</t>
+    <t>Subdomain matches /^[a-z0-9-]+$/ and contains 'my' and 'eatery' (e.g., 'my-eatery-42'); the field has the readonly attribute</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -789,26 +808,29 @@
     <t>Step 2 — password validation (mismatch)</t>
   </si>
   <si>
-    <t>Step 2 rejects mismatching Password and Confirm Password values</t>
-  </si>
-  <si>
-    <t>Step 2 'Set Password' is visible (step 1 completed)</t>
+    <t>Step 2 does NOT submit when Password and Confirm Password differ</t>
+  </si>
+  <si>
+    <t>Step 2 'Set Password' visible (step 1 completed)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter 'TestPass!2025' in Password
-2. Enter 'DifferentPass!2025' in Confirm Password
+2. Enter 'DifferentTestPass!2025' in Confirm Password
 3. Check the Terms checkbox
 4. Attempt to click 'Create Account'</t>
   </si>
   <si>
     <t xml:space="preserve">Password: TestPass!2025
-Confirm Password: DifferentPass!2025</t>
-  </si>
-  <si>
-    <t>Validation message: 'Passwords do not match'; Create Account is disabled OR submission is blocked</t>
+Confirm Password: DifferentTestPass!2025</t>
+  </si>
+  <si>
+    <t>Form does not submit; URL stays on /signup; step-2 heading still visible</t>
   </si>
   <si>
     <t>User remains on step 2</t>
+  </si>
+  <si>
+    <t>Passed in 5.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-09</t>
@@ -848,13 +870,16 @@
   <si>
     <t xml:space="preserve">1. Fill Password and Confirm Password with valid matching values
 2. Leave the Terms checkbox UNCHECKED
-3. Observe the Create Account button state</t>
+3. Inspect the Create Account button state</t>
   </si>
   <si>
     <t>Terms checkbox: unchecked</t>
   </si>
   <si>
-    <t>Create Account button is disabled; cannot be clicked</t>
+    <t>Create Account button is disabled (cannot be clicked); Terms checkbox is unchecked</t>
+  </si>
+  <si>
+    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-01</t>
@@ -863,15 +888,17 @@
     <t>Step 1 — read-only fields</t>
   </si>
   <si>
-    <t>Subdomain, Location Name, and Address fields are read-only and cannot be edited by clicking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open DevTools → Elements
-2. Confirm each of #subDomain, #locationName, #locationAddress has the readonly attribute
-3. Click into each and attempt to type</t>
-  </si>
-  <si>
-    <t>None of the three fields accept keyboard input; the readonly attribute is set on the input elements</t>
+    <t>Subdomain, Location Name, and Address fields are read-only and cannot be edited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Inspect each of #subDomain, #locationName, #locationAddress
+2. Confirm each has the readonly attribute</t>
+  </si>
+  <si>
+    <t>All three inputs have the readonly attribute set; values cannot be edited by typing</t>
+  </si>
+  <si>
+    <t>Passed in 3.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -900,19 +927,18 @@
     <t>Step 2 — password visibility toggle</t>
   </si>
   <si>
-    <t>Both Password and Confirm Password fields have a working show/hide toggle</t>
+    <t>Show/Hide password button toggles the input type</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type into Password
-2. Click the 'Show password' button next to Password
-3. Click again to re-mask
-4. Repeat for Confirm Password</t>
-  </si>
-  <si>
-    <t>Password: TestPass!2025</t>
-  </si>
-  <si>
-    <t>Each show-password button toggles the corresponding field between type='password' and type='text'; mask state is independent for the two fields</t>
+2. Click the 'Show password' button
+3. Click again to re-mask</t>
+  </si>
+  <si>
+    <t>First click: type becomes 'text'; second click: type returns to 'password'</t>
+  </si>
+  <si>
+    <t>Passed in 3.3s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-04</t>
@@ -931,10 +957,10 @@
 2. Inspect each step-1 field</t>
   </si>
   <si>
-    <t>Step 1 reappears; all editable fields retain the values entered previously (no data loss)</t>
-  </si>
-  <si>
-    <t>User can navigate back and forth between steps without losing input</t>
+    <t>Step 1 reappears; all editable fields retain previously entered values</t>
+  </si>
+  <si>
+    <t>User can navigate back and forth without losing input</t>
   </si>
   <si>
     <t>SignUp-001-NAV-01</t>
@@ -949,7 +975,7 @@
     <t>1. Click the 'Sign in' link below the form</t>
   </si>
   <si>
-    <t>Browser navigates to /login</t>
+    <t>Link href ends with /login; browser navigates to /login</t>
   </si>
   <si>
     <t>User on the login screen</t>
@@ -958,16 +984,13 @@
     <t>SignUp-001-NAV-02</t>
   </si>
   <si>
-    <t>'← Back' link navigates to /</t>
-  </si>
-  <si>
     <t>1. Click the '← Back' link</t>
   </si>
   <si>
-    <t>Browser navigates to the homepage</t>
-  </si>
-  <si>
-    <t>User on the homepage</t>
+    <t>Link href is '/'; browser navigates to the homepage</t>
+  </si>
+  <si>
+    <t>Passed in 2.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -987,7 +1010,7 @@
     <t>Restaurant Name: '   My Eatery   '</t>
   </si>
   <si>
-    <t>App trims whitespace before deriving the subdomain; subdomain is 'myeatery' not 'my-eatery'</t>
+    <t>App trims whitespace before deriving the subdomain</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-02</t>
@@ -1003,7 +1026,7 @@
     <t>Restaurant Name: My Eatery &amp; Café (2026)!</t>
   </si>
   <si>
-    <t>Subdomain is derived to a URL-safe slug (alphanumeric + dashes only): e.g., 'myeaterycafe2026'; no special characters leak into the subdomain</t>
+    <t>Subdomain is derived to a URL-safe slug; no special characters leak</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-03</t>
@@ -1012,14 +1035,14 @@
     <t>Disposable email (yopmail) is accepted (or rejected with clear message)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Use a yopmail address (e.g., arslan.moon+test@yopmail.com)
+    <t xml:space="preserve">1. Use a yopmail address
 2. Complete signup</t>
   </si>
   <si>
     <t>Email: arslan.moon+test&lt;ts&gt;@yopmail.com</t>
   </si>
   <si>
-    <t>App either (a) accepts the email and proceeds with signup, or (b) explicitly rejects with 'Disposable email addresses are not allowed'. Silent failure is not acceptable.</t>
+    <t>App either accepts the email and proceeds, or explicitly rejects with a clear message</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-04</t>
@@ -1031,17 +1054,17 @@
     <t>An account 'demo' already exists; new user tries Restaurant Name 'Demo'</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Enter 'Demo' as Restaurant Name (auto-derives to existing subdomain 'demo')
-2. Complete the full form and click Create Account</t>
-  </si>
-  <si>
-    <t>Restaurant Name: Demo (collides with existing tenant)</t>
-  </si>
-  <si>
-    <t>Server rejects the registration with a clear message: 'Subdomain already in use' or similar; URL stays on /signup</t>
-  </si>
-  <si>
-    <t>No duplicate tenant created</t>
+    <t xml:space="preserve">1. Enter 'Demo' as Restaurant Name (collides with existing tenant)
+2. Complete the form and click Create Account</t>
+  </si>
+  <si>
+    <t>Restaurant Name: Demo</t>
+  </si>
+  <si>
+    <t>Server rejects with 'Subdomain already in use' or similar</t>
+  </si>
+  <si>
+    <t>No duplicate tenant</t>
   </si>
   <si>
     <t>SignUp-001-SEC-01</t>
@@ -1050,14 +1073,14 @@
     <t>Signup security</t>
   </si>
   <si>
-    <t>Password fields use type='password' (masked, not in DOM as plaintext)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect both Password and Confirm Password inputs in DevTools
-2. Confirm their initial type attribute</t>
-  </si>
-  <si>
-    <t>Both inputs default to type='password'; values are masked in the DOM by default</t>
+    <t>Password fields use type='password' (masked in DOM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Inspect Password and Confirm Password inputs
+2. Confirm initial type attribute</t>
+  </si>
+  <si>
+    <t>Both inputs default to type='password'</t>
   </si>
   <si>
     <t>SignUp-001-SEC-02</t>
@@ -1068,10 +1091,10 @@
   <si>
     <t xml:space="preserve">1. Open DevTools → Network
 2. Submit the form
-3. Inspect the request URL and protocol</t>
-  </si>
-  <si>
-    <t>The form-submit request goes to an https:// endpoint; no plaintext HTTP credentials in transit</t>
+3. Inspect the request protocol</t>
+  </si>
+  <si>
+    <t>Form submission goes to an https:// endpoint</t>
   </si>
   <si>
     <t>SignUp-001-SEC-03</t>
@@ -1081,16 +1104,16 @@
   </si>
   <si>
     <t xml:space="preserve">1. Enter '&lt;script&gt;alert(1)&lt;/script&gt;' as Restaurant Name
-2. Complete signup and observe the post-signup screen 'Restaurant: &lt;name&gt;' paragraph</t>
+2. Complete signup and observe the post-signup screen</t>
   </si>
   <si>
     <t>Restaurant Name: &lt;script&gt;alert(1)&lt;/script&gt;</t>
   </si>
   <si>
-    <t>No JS alert fires; the value is either rejected at input validation OR rendered as escaped text (no HTML injection)</t>
-  </si>
-  <si>
-    <t>n/a — XSS does not execute</t>
+    <t>No alert fires; value is escaped or rejected</t>
+  </si>
+  <si>
+    <t>XSS does not execute</t>
   </si>
   <si>
     <t>SignUp-001-SEC-04</t>
@@ -1102,12 +1125,14 @@
     <t>Successful signup just completed</t>
   </si>
   <si>
-    <t xml:space="preserve">1. After Create Account succeeds, open DevTools
-2. Search the DOM for the password string
-3. Inspect the network response for any password field</t>
-  </si>
-  <si>
-    <t>Password string does NOT appear anywhere in the DOM or in any HTTP response body. (Only the hashed/transient form submission contained it.)</t>
+    <t xml:space="preserve">1. Open DevTools after Create Account succeeds
+2. Search DOM and HTTP responses for the password string</t>
+  </si>
+  <si>
+    <t>Password: TestPass!2025</t>
+  </si>
+  <si>
+    <t>Password does NOT appear in DOM or any HTTP response body</t>
   </si>
   <si>
     <t>Password not leaked</t>
@@ -1615,13 +1640,13 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1644,13 +1669,13 @@
         <v>26</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -1673,13 +1698,13 @@
         <v>48</v>
       </c>
       <c r="D4" s="4">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E4" s="4">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -1806,8 +1831,8 @@
       <c r="I3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>4</v>
+      <c r="J3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1836,295 +1861,295 @@
         <v>52</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>4</v>
+        <v>53</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>4</v>
+        <v>61</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>4</v>
+        <v>68</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>4</v>
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>4</v>
+        <v>81</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>4</v>
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>4</v>
+        <v>94</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>4</v>
+        <v>101</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>4</v>
+        <v>108</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>4</v>
@@ -2132,127 +2157,127 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>4</v>
+        <v>121</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>4</v>
+        <v>127</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>4</v>
+        <v>53</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>4</v>
@@ -2260,31 +2285,31 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>4</v>
@@ -2292,31 +2317,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>4</v>
@@ -2324,63 +2349,63 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>4</v>
+        <v>94</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>4</v>
@@ -2388,31 +2413,31 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>4</v>
@@ -2420,31 +2445,31 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -2507,31 +2532,31 @@
     </row>
     <row r="2" ht="98" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>12</v>
@@ -2539,31 +2564,31 @@
     </row>
     <row r="3" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>12</v>
@@ -2571,63 +2596,63 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>4</v>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>4</v>
@@ -2635,95 +2660,95 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>4</v>
+        <v>189</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>4</v>
+        <v>189</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>4</v>
@@ -2731,31 +2756,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>4</v>
@@ -2763,95 +2788,95 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>4</v>
+      <c r="J10" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>4</v>
+        <v>242</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>4</v>
@@ -2859,159 +2884,159 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>4</v>
+        <v>257</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>4</v>
+        <v>263</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>263</v>
+        <v>99</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>4</v>
+        <v>275</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>4</v>
@@ -3019,95 +3044,95 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>4</v>
+      <c r="J18" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>279</v>
+        <v>129</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>4</v>
+        <v>292</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>4</v>
@@ -3115,31 +3140,31 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>4</v>
@@ -3147,31 +3172,31 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>4</v>
@@ -3179,31 +3204,31 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -3211,63 +3236,63 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>4</v>
+        <v>275</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>4</v>
@@ -3275,31 +3300,31 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>4</v>
@@ -3307,31 +3332,31 @@
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>4</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="338">
   <si>
     <t>FEATURE</t>
   </si>
@@ -36,6 +36,9 @@
     <t>FAILED</t>
   </si>
   <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
     <t>LAST RUN</t>
   </si>
   <si>
@@ -48,7 +51,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 13:23:58</t>
+    <t>2026-06-26 14:02:03</t>
   </si>
   <si>
     <t>PASS</t>
@@ -124,7 +127,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>Passed in 4.5s on chromium.</t>
+    <t>Passed in 6.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -155,7 +158,7 @@
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
-    <t>Passed in 4.1s on chromium.</t>
+    <t>Passed in 3.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -186,7 +189,7 @@
     <t>User is NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 3.8s on chromium.</t>
+    <t>Passed in 4.8s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -214,7 +217,7 @@
     <t>User remains on /Login; no authentication</t>
   </si>
   <si>
-    <t>Passed in 5.1s on chromium.</t>
+    <t>Passed in 3.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -239,7 +242,7 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 8.1s on chromium.</t>
+    <t>Passed in 3.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-05</t>
@@ -260,7 +263,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 5.6s on chromium.</t>
+    <t>Passed in 3.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -285,7 +288,7 @@
     <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
   </si>
   <si>
-    <t>Passed in 4.2s on chromium.</t>
+    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -307,7 +310,7 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 4.8s on chromium.</t>
+    <t>Passed in 3.5s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-01</t>
@@ -327,9 +330,6 @@
   </si>
   <si>
     <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
-  </si>
-  <si>
-    <t>Passed in 3.2s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -352,9 +352,6 @@
     <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
   </si>
   <si>
-    <t>Passed in 4.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -375,7 +372,7 @@
     <t>User is signed in</t>
   </si>
   <si>
-    <t>Passed in 4.0s on chromium.</t>
+    <t>Passed in 5.4s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-04</t>
@@ -417,7 +414,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 3.5s on chromium.</t>
+    <t>Passed in 2.8s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -436,7 +433,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
+    <t>Passed in 2.6s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -453,6 +450,9 @@
   </si>
   <si>
     <t>User on the homepage</t>
+  </si>
+  <si>
+    <t>Passed in 2.7s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -621,7 +621,10 @@
     <t>New tenant created; user proceeds to /select-location</t>
   </si>
   <si>
-    <t>Passed in 6.3s on chromium.</t>
+    <t>Skipped.</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>SignUp-001-AC2-POS-01</t>
@@ -653,9 +656,6 @@
     <t>Registration confirmed end-to-end</t>
   </si>
   <si>
-    <t>Passed in 4.4s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-01</t>
   </si>
   <si>
@@ -681,6 +681,9 @@
   </si>
   <si>
     <t>User remains on step 1</t>
+  </si>
+  <si>
+    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-02</t>
@@ -830,9 +833,6 @@
     <t>User remains on step 2</t>
   </si>
   <si>
-    <t>Passed in 5.4s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-09</t>
   </si>
   <si>
@@ -879,7 +879,7 @@
     <t>Create Account button is disabled (cannot be clicked); Terms checkbox is unchecked</t>
   </si>
   <si>
-    <t>Passed in 2.9s on chromium.</t>
+    <t>Passed in 3.3s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-01</t>
@@ -898,7 +898,7 @@
     <t>All three inputs have the readonly attribute set; values cannot be edited by typing</t>
   </si>
   <si>
-    <t>Passed in 3.4s on chromium.</t>
+    <t>Passed in 4.1s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -938,7 +938,7 @@
     <t>First click: type becomes 'text'; second click: type returns to 'password'</t>
   </si>
   <si>
-    <t>Passed in 3.3s on chromium.</t>
+    <t>Passed in 4.6s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-04</t>
@@ -981,6 +981,9 @@
     <t>User on the login screen</t>
   </si>
   <si>
+    <t>Passed in 4.4s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NAV-02</t>
   </si>
   <si>
@@ -988,9 +991,6 @@
   </si>
   <si>
     <t>Link href is '/'; browser navigates to the homepage</t>
-  </si>
-  <si>
-    <t>Passed in 2.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -1142,7 +1142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1177,8 +1177,14 @@
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF6C757D"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1203,6 +1209,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9ECEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1233,7 +1244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1248,6 +1259,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1589,18 +1603,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="5" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1628,13 +1642,16 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2">
         <v>22</v>
@@ -1651,19 +1668,22 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2">
         <v>26</v>
@@ -1675,24 +1695,27 @@
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4">
         <v>48</v>
@@ -1704,16 +1727,19 @@
         <v>20</v>
       </c>
       <c r="F4" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>16</v>
+      <c r="H4" s="4">
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1741,322 +1767,322 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2064,7 +2090,7 @@
         <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>96</v>
@@ -2082,74 +2108,74 @@
         <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>4</v>
@@ -2157,98 +2183,98 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2262,7 +2288,7 @@
         <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>136</v>
@@ -2274,10 +2300,10 @@
         <v>138</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>4</v>
@@ -2294,7 +2320,7 @@
         <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>141</v>
@@ -2306,10 +2332,10 @@
         <v>143</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>4</v>
@@ -2326,7 +2352,7 @@
         <v>145</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>146</v>
@@ -2338,10 +2364,10 @@
         <v>148</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>4</v>
@@ -2358,25 +2384,25 @@
         <v>151</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>153</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2390,13 +2416,13 @@
         <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>157</v>
@@ -2405,7 +2431,7 @@
         <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>4</v>
@@ -2422,7 +2448,7 @@
         <v>160</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>161</v>
@@ -2437,7 +2463,7 @@
         <v>164</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>4</v>
@@ -2469,7 +2495,7 @@
         <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -2500,37 +2526,37 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" ht="98" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" ht="112" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>172</v>
       </c>
@@ -2558,40 +2584,40 @@
       <c r="I2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2620,39 +2646,39 @@
         <v>197</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>198</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>4</v>
@@ -2660,95 +2686,95 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>4</v>
@@ -2756,31 +2782,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>4</v>
@@ -2788,66 +2814,66 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>242</v>
+        <v>88</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2873,10 +2899,10 @@
         <v>249</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>4</v>
@@ -2905,13 +2931,13 @@
         <v>256</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>257</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2925,25 +2951,25 @@
         <v>260</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>261</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>262</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>263</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2963,16 +2989,16 @@
         <v>268</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>4</v>
@@ -3001,13 +3027,13 @@
         <v>274</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>275</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3027,7 +3053,7 @@
         <v>280</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>281</v>
@@ -3036,7 +3062,7 @@
         <v>282</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>4</v>
@@ -3053,13 +3079,13 @@
         <v>285</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>286</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>287</v>
@@ -3068,42 +3094,42 @@
         <v>288</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>284</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3117,7 +3143,7 @@
         <v>295</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>296</v>
@@ -3129,10 +3155,10 @@
         <v>298</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>4</v>
@@ -3149,7 +3175,7 @@
         <v>300</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>301</v>
@@ -3161,10 +3187,10 @@
         <v>303</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>4</v>
@@ -3181,7 +3207,7 @@
         <v>305</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>306</v>
@@ -3193,10 +3219,10 @@
         <v>308</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>4</v>
@@ -3228,7 +3254,7 @@
         <v>315</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -3251,19 +3277,19 @@
         <v>319</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>320</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>275</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3277,22 +3303,22 @@
         <v>322</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>323</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>324</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>4</v>
@@ -3309,7 +3335,7 @@
         <v>326</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>327</v>
@@ -3324,7 +3350,7 @@
         <v>330</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>4</v>
@@ -3356,7 +3382,7 @@
         <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>4</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="336">
   <si>
     <t>FEATURE</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 14:02:03</t>
+    <t>2026-06-26 14:35:03</t>
   </si>
   <si>
     <t>PASS</t>
@@ -127,7 +127,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>Passed in 6.0s on chromium.</t>
+    <t>Passed in 3.6s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -158,7 +158,7 @@
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
-    <t>Passed in 3.9s on chromium.</t>
+    <t>Passed in 3.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -189,7 +189,7 @@
     <t>User is NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 4.8s on chromium.</t>
+    <t>Passed in 3.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -217,7 +217,7 @@
     <t>User remains on /Login; no authentication</t>
   </si>
   <si>
-    <t>Passed in 3.7s on chromium.</t>
+    <t>Passed in 5.5s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -242,9 +242,6 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 3.1s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -263,7 +260,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
+    <t>Passed in 3.2s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -288,7 +285,7 @@
     <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
   </si>
   <si>
-    <t>Passed in 2.9s on chromium.</t>
+    <t>Passed in 5.2s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -310,7 +307,7 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 3.5s on chromium.</t>
+    <t>Passed in 2.7s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-01</t>
@@ -330,6 +327,9 @@
   </si>
   <si>
     <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
+  </si>
+  <si>
+    <t>Passed in 2.4s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -352,6 +352,9 @@
     <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
   </si>
   <si>
+    <t>Passed in 4.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -372,9 +375,6 @@
     <t>User is signed in</t>
   </si>
   <si>
-    <t>Passed in 5.4s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -414,7 +414,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 2.8s on chromium.</t>
+    <t>Passed in 3.0s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -433,7 +433,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 2.6s on chromium.</t>
+    <t>Passed in 3.4s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -452,7 +452,7 @@
     <t>User on the homepage</t>
   </si>
   <si>
-    <t>Passed in 2.7s on chromium.</t>
+    <t>Passed in 2.8s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -683,9 +683,6 @@
     <t>User remains on step 1</t>
   </si>
   <si>
-    <t>Passed in 4.0s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-02</t>
   </si>
   <si>
@@ -714,6 +711,9 @@
   </si>
   <si>
     <t>Business Email: (empty)</t>
+  </si>
+  <si>
+    <t>Passed in 2.6s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-04</t>
@@ -879,7 +879,7 @@
     <t>Create Account button is disabled (cannot be clicked); Terms checkbox is unchecked</t>
   </si>
   <si>
-    <t>Passed in 3.3s on chromium.</t>
+    <t>Passed in 3.1s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-01</t>
@@ -898,7 +898,7 @@
     <t>All three inputs have the readonly attribute set; values cannot be edited by typing</t>
   </si>
   <si>
-    <t>Passed in 4.1s on chromium.</t>
+    <t>Passed in 2.1s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -938,9 +938,6 @@
     <t>First click: type becomes 'text'; second click: type returns to 'password'</t>
   </si>
   <si>
-    <t>Passed in 4.6s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-UI-04</t>
   </si>
   <si>
@@ -979,9 +976,6 @@
   </si>
   <si>
     <t>User on the login screen</t>
-  </si>
-  <si>
-    <t>Passed in 4.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NAV-02</t>
@@ -1951,7 +1945,7 @@
         <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1959,22 +1953,22 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>60</v>
@@ -1983,7 +1977,7 @@
         <v>68</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -1991,31 +1985,31 @@
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2023,31 +2017,31 @@
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2055,31 +2049,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2090,7 +2084,7 @@
         <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>96</v>
@@ -2108,10 +2102,10 @@
         <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2119,31 +2113,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2166,13 +2160,13 @@
         <v>111</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>112</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>113</v>
@@ -2198,7 +2192,7 @@
         <v>117</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>118</v>
@@ -2230,7 +2224,7 @@
         <v>123</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>124</v>
@@ -2262,7 +2256,7 @@
         <v>129</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>130</v>
@@ -2300,7 +2294,7 @@
         <v>138</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>113</v>
@@ -2332,7 +2326,7 @@
         <v>143</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>113</v>
@@ -2390,16 +2384,16 @@
         <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>153</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2646,7 +2640,7 @@
         <v>197</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2654,25 +2648,25 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>197</v>
@@ -2686,31 +2680,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2835,10 +2829,10 @@
         <v>234</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2870,7 +2864,7 @@
         <v>242</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2957,13 +2951,13 @@
         <v>261</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>262</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>263</v>
@@ -2989,13 +2983,13 @@
         <v>268</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>113</v>
@@ -3027,10 +3021,10 @@
         <v>274</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -3038,28 +3032,28 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>113</v>
@@ -3070,31 +3064,31 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>289</v>
+        <v>94</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3102,10 +3096,10 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>128</v>
@@ -3114,19 +3108,19 @@
         <v>211</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>289</v>
+        <v>36</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3134,28 +3128,28 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>113</v>
@@ -3166,28 +3160,28 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>113</v>
@@ -3198,28 +3192,28 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>113</v>
@@ -3230,28 +3224,28 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>113</v>
@@ -3262,31 +3256,31 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>246</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3294,28 +3288,28 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>113</v>
@@ -3326,28 +3320,28 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>113</v>
@@ -3358,28 +3352,28 @@
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>113</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -51,7 +51,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 14:35:03</t>
+    <t>2026-06-26 15:01:15</t>
   </si>
   <si>
     <t>PASS</t>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>SignUp-001</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -127,7 +133,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>Passed in 3.6s on chromium.</t>
+    <t>Passed in 3.5s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -158,7 +164,7 @@
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
-    <t>Passed in 3.7s on chromium.</t>
+    <t>Passed in 16.6s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -189,7 +195,7 @@
     <t>User is NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 3.9s on chromium.</t>
+    <t>Passed in 19.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -217,7 +223,7 @@
     <t>User remains on /Login; no authentication</t>
   </si>
   <si>
-    <t>Passed in 5.5s on chromium.</t>
+    <t>Passed in 15.6s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -242,6 +248,9 @@
     <t>User remains on /Login</t>
   </si>
   <si>
+    <t>Passed in 15.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -260,7 +269,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 3.2s on chromium.</t>
+    <t>Passed in 17.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -285,7 +294,7 @@
     <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
   </si>
   <si>
-    <t>Passed in 5.2s on chromium.</t>
+    <t>Passed in 3.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -307,7 +316,7 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 2.7s on chromium.</t>
+    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-01</t>
@@ -329,7 +338,7 @@
     <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
   </si>
   <si>
-    <t>Passed in 2.4s on chromium.</t>
+    <t>Passed in 4.6s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -352,7 +361,7 @@
     <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
   </si>
   <si>
-    <t>Passed in 4.8s on chromium.</t>
+    <t>Passed in 3.1s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-03</t>
@@ -375,6 +384,9 @@
     <t>User is signed in</t>
   </si>
   <si>
+    <t>Passed in 3.4s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -414,7 +426,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
+    <t>Passed in 15.0s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -433,7 +445,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 3.4s on chromium.</t>
+    <t>Passed in 14.9s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -452,7 +464,7 @@
     <t>User on the homepage</t>
   </si>
   <si>
-    <t>Passed in 2.8s on chromium.</t>
+    <t>Passed in 15.1s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -621,10 +633,7 @@
     <t>New tenant created; user proceeds to /select-location</t>
   </si>
   <si>
-    <t>Skipped.</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>SignUp-001-AC2-POS-01</t>
@@ -713,9 +722,6 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
-    <t>Passed in 2.6s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
@@ -879,9 +885,6 @@
     <t>Create Account button is disabled (cannot be clicked); Terms checkbox is unchecked</t>
   </si>
   <si>
-    <t>Passed in 3.1s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-UI-01</t>
   </si>
   <si>
@@ -896,9 +899,6 @@
   </si>
   <si>
     <t>All three inputs have the readonly attribute set; values cannot be edited by typing</t>
-  </si>
-  <si>
-    <t>Passed in 2.1s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -1162,18 +1162,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF856404"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF4338CA"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF6C757D"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -1197,17 +1197,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9ECEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1250,10 +1250,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1689,51 +1689,51 @@
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5">
         <v>48</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>28</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>20</v>
       </c>
-      <c r="F4" s="4">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="F4" s="5">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5">
         <v>0</v>
       </c>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1761,63 +1761,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1825,31 +1825,31 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -1857,31 +1857,31 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -1889,31 +1889,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -1921,31 +1921,31 @@
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1953,31 +1953,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -1985,31 +1985,31 @@
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2017,31 +2017,31 @@
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2049,31 +2049,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2081,31 +2081,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2113,31 +2113,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2145,63 +2145,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2209,31 +2209,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2241,31 +2241,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2273,127 +2273,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2401,97 +2401,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2520,450 +2520,450 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="112" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>181</v>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2983,18 +2983,18 @@
         <v>268</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3009,25 +3009,25 @@
         <v>272</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>273</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3047,7 +3047,7 @@
         <v>279</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>280</v>
@@ -3056,9 +3056,9 @@
         <v>281</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3073,13 +3073,13 @@
         <v>284</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>285</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>286</v>
@@ -3088,10 +3088,10 @@
         <v>287</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3102,28 +3102,28 @@
         <v>283</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>289</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>290</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3137,7 +3137,7 @@
         <v>293</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>294</v>
@@ -3149,12 +3149,12 @@
         <v>296</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
         <v>298</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>299</v>
@@ -3181,12 +3181,12 @@
         <v>301</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
         <v>303</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>304</v>
@@ -3213,12 +3213,12 @@
         <v>306</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3248,9 +3248,9 @@
         <v>313</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3265,25 +3265,25 @@
         <v>316</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>317</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>318</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3297,24 +3297,24 @@
         <v>320</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>321</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>322</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
         <v>324</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>325</v>
@@ -3344,9 +3344,9 @@
         <v>328</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3376,9 +3376,9 @@
         <v>335</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="333">
   <si>
     <t>FEATURE</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 15:01:15</t>
+    <t>2026-06-26 15:08:26</t>
   </si>
   <si>
     <t>PASS</t>
@@ -133,7 +133,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>Passed in 3.5s on chromium.</t>
+    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -164,7 +164,7 @@
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
-    <t>Passed in 16.6s on chromium.</t>
+    <t>Passed in 4.5s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -195,7 +195,7 @@
     <t>User is NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 19.3s on chromium.</t>
+    <t>Passed in 4.4s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -223,7 +223,7 @@
     <t>User remains on /Login; no authentication</t>
   </si>
   <si>
-    <t>Passed in 15.6s on chromium.</t>
+    <t>Passed in 6.8s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -248,7 +248,7 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 15.8s on chromium.</t>
+    <t>Passed in 4.8s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-05</t>
@@ -269,7 +269,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 17.7s on chromium.</t>
+    <t>Passed in 4.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -294,7 +294,7 @@
     <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
+    <t>Passed in 3.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -316,9 +316,6 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 2.9s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -338,7 +335,7 @@
     <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
   </si>
   <si>
-    <t>Passed in 4.6s on chromium.</t>
+    <t>Passed in 3.0s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -361,7 +358,7 @@
     <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
   </si>
   <si>
-    <t>Passed in 3.1s on chromium.</t>
+    <t>Passed in 3.5s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-03</t>
@@ -384,9 +381,6 @@
     <t>User is signed in</t>
   </si>
   <si>
-    <t>Passed in 3.4s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -426,7 +420,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 15.0s on chromium.</t>
+    <t>Passed in 3.6s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -445,7 +439,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 14.9s on chromium.</t>
+    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -462,9 +456,6 @@
   </si>
   <si>
     <t>User on the homepage</t>
-  </si>
-  <si>
-    <t>Passed in 15.1s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -2041,7 +2032,7 @@
         <v>70</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2049,31 +2040,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2081,31 +2072,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2113,31 +2104,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2145,31 +2136,31 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>4</v>
@@ -2177,31 +2168,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2209,31 +2200,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2241,31 +2232,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2273,31 +2264,31 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>4</v>
@@ -2305,31 +2296,31 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>4</v>
@@ -2337,31 +2328,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>4</v>
@@ -2369,31 +2360,31 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2401,31 +2392,31 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>4</v>
@@ -2433,31 +2424,31 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>4</v>
@@ -2465,31 +2456,31 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>4</v>
@@ -2552,31 +2543,31 @@
     </row>
     <row r="2" ht="112" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>17</v>
@@ -2584,31 +2575,31 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>17</v>
@@ -2616,31 +2607,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>17</v>
@@ -2648,31 +2639,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>4</v>
@@ -2680,31 +2671,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>17</v>
@@ -2712,31 +2703,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>17</v>
@@ -2744,31 +2735,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>4</v>
@@ -2776,31 +2767,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>4</v>
@@ -2808,31 +2799,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>17</v>
@@ -2840,31 +2831,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>17</v>
@@ -2872,31 +2863,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>4</v>
@@ -2904,31 +2895,31 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>17</v>
@@ -2936,31 +2927,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>17</v>
@@ -2968,31 +2959,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>4</v>
@@ -3000,31 +2991,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>17</v>
@@ -3032,31 +3023,31 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>4</v>
@@ -3064,31 +3055,31 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>17</v>
@@ -3096,31 +3087,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>17</v>
@@ -3128,31 +3119,31 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>4</v>
@@ -3160,31 +3151,31 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>4</v>
@@ -3192,31 +3183,31 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>4</v>
@@ -3224,31 +3215,31 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>4</v>
@@ -3256,31 +3247,31 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>17</v>
@@ -3288,31 +3279,31 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>4</v>
@@ -3320,31 +3311,31 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>4</v>
@@ -3352,31 +3343,31 @@
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>335</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>4</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="320">
   <si>
     <t>FEATURE</t>
   </si>
@@ -51,22 +51,16 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 15:08:26</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>user-signup</t>
   </si>
   <si>
     <t>SignUp-001</t>
-  </si>
-  <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -133,7 +127,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>Passed in 4.0s on chromium.</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -164,9 +158,6 @@
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
-    <t>Passed in 4.5s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -195,9 +186,6 @@
     <t>User is NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 4.4s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -223,9 +211,6 @@
     <t>User remains on /Login; no authentication</t>
   </si>
   <si>
-    <t>Passed in 6.8s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -248,9 +233,6 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 4.8s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -267,9 +249,6 @@
   <si>
     <t xml:space="preserve">Email: (empty)
 Password: (empty)</t>
-  </si>
-  <si>
-    <t>Passed in 4.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -294,9 +273,6 @@
     <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
   </si>
   <si>
-    <t>Passed in 3.3s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -335,9 +311,6 @@
     <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-02</t>
   </si>
   <si>
@@ -358,9 +331,6 @@
     <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
   </si>
   <si>
-    <t>Passed in 3.5s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -420,9 +390,6 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 3.6s on chromium.</t>
-  </si>
-  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -437,9 +404,6 @@
   </si>
   <si>
     <t>User on the signup screen</t>
-  </si>
-  <si>
-    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -624,9 +588,6 @@
     <t>New tenant created; user proceeds to /select-location</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
-  </si>
-  <si>
     <t>SignUp-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1127,7 +1088,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1143,12 +1104,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF155724"/>
-      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1169,7 +1124,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1179,11 +1134,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A8FB8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1229,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1241,12 +1191,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1648,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1689,42 +1636,42 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>48</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>28</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>20</v>
       </c>
-      <c r="F4" s="5">
-        <v>15</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="5">
+      <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>19</v>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1752,63 +1699,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1816,31 +1763,31 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -1848,31 +1795,31 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -1880,31 +1827,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -1912,31 +1859,31 @@
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1944,31 +1891,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -1976,31 +1923,31 @@
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2008,31 +1955,31 @@
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2040,31 +1987,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2072,31 +2019,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2104,31 +2051,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2136,63 +2083,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2200,31 +2147,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2232,31 +2179,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2264,127 +2211,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2392,97 +2339,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2511,865 +2458,865 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" ht="112" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J27" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="341">
   <si>
     <t>FEATURE</t>
   </si>
@@ -51,10 +51,10 @@
     <t>Login</t>
   </si>
   <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
+    <t>2026-06-26 22:00:46</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -127,7 +127,7 @@
     <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
+    <t>Passed in 4.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -158,6 +158,9 @@
     <t>User is NOT authenticated; no session cookie set</t>
   </si>
   <si>
+    <t>Passed in 7.2s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -186,6 +189,9 @@
     <t>User is NOT authenticated</t>
   </si>
   <si>
+    <t>Passed in 9.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -211,6 +217,9 @@
     <t>User remains on /Login; no authentication</t>
   </si>
   <si>
+    <t>Passed in 5.7s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -233,6 +242,9 @@
     <t>User remains on /Login</t>
   </si>
   <si>
+    <t>Passed in 6.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -249,6 +261,9 @@
   <si>
     <t xml:space="preserve">Email: (empty)
 Password: (empty)</t>
+  </si>
+  <si>
+    <t>Passed in 6.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -273,6 +288,9 @@
     <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
   </si>
   <si>
+    <t>Passed in 3.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -311,6 +329,9 @@
     <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
   </si>
   <si>
+    <t>Passed in 4.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-02</t>
   </si>
   <si>
@@ -331,6 +352,9 @@
     <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
   </si>
   <si>
+    <t>Passed in 3.0s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -351,6 +375,9 @@
     <t>User is signed in</t>
   </si>
   <si>
+    <t>Passed in 5.8s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -390,6 +417,9 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
+    <t>Passed in 5.6s on chromium.</t>
+  </si>
+  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -420,6 +450,9 @@
   </si>
   <si>
     <t>User on the homepage</t>
+  </si>
+  <si>
+    <t>Passed in 5.2s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -588,6 +621,12 @@
     <t>New tenant created; user proceeds to /select-location</t>
   </si>
   <si>
+    <t>Skipped.</t>
+  </si>
+  <si>
+    <t>SKIP</t>
+  </si>
+  <si>
     <t>SignUp-001-AC2-POS-01</t>
   </si>
   <si>
@@ -644,6 +683,9 @@
     <t>User remains on step 1</t>
   </si>
   <si>
+    <t>Passed in 3.7s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NEG-02</t>
   </si>
   <si>
@@ -674,6 +716,9 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
+    <t>Passed in 3.4s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
@@ -697,6 +742,9 @@
     <t>input[type=email] reports typeMismatch validity; form does not advance</t>
   </si>
   <si>
+    <t>Passed in 5.9s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NEG-05</t>
   </si>
   <si>
@@ -761,6 +809,9 @@
   </si>
   <si>
     <t>Subdomain matches /^[a-z0-9-]+$/ and contains 'my' and 'eatery' (e.g., 'my-eatery-42'); the field has the readonly attribute</t>
+  </si>
+  <si>
+    <t>Passed in 4.3s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -837,6 +888,9 @@
     <t>Create Account button is disabled (cannot be clicked); Terms checkbox is unchecked</t>
   </si>
   <si>
+    <t>Passed in 4.4s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-UI-01</t>
   </si>
   <si>
@@ -851,6 +905,9 @@
   </si>
   <si>
     <t>All three inputs have the readonly attribute set; values cannot be edited by typing</t>
+  </si>
+  <si>
+    <t>Passed in 3.6s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -890,6 +947,9 @@
     <t>First click: type becomes 'text'; second click: type returns to 'password'</t>
   </si>
   <si>
+    <t>Passed in 4.1s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-UI-04</t>
   </si>
   <si>
@@ -928,6 +988,9 @@
   </si>
   <si>
     <t>User on the login screen</t>
+  </si>
+  <si>
+    <t>Passed in 2.8s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NAV-02</t>
@@ -1088,7 +1151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1108,7 +1171,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF856404"/>
+      <color rgb="FF155724"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -1123,8 +1186,14 @@
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF6C757D"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1138,7 +1207,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1149,6 +1218,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9ECEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1179,7 +1253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1194,6 +1268,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1595,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1627,13 +1704,13 @@
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>12</v>
@@ -1659,13 +1736,13 @@
         <v>20</v>
       </c>
       <c r="F4" s="4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>17</v>
@@ -1787,7 +1864,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -1795,31 +1872,31 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -1827,31 +1904,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -1859,31 +1936,31 @@
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1891,31 +1968,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -1923,31 +2000,31 @@
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -1955,31 +2032,31 @@
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -1987,31 +2064,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2019,31 +2096,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2051,31 +2128,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2083,31 +2160,31 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>4</v>
@@ -2115,31 +2192,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2147,31 +2224,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2179,31 +2256,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2211,31 +2288,31 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>4</v>
@@ -2243,31 +2320,31 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>4</v>
@@ -2275,31 +2352,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>4</v>
@@ -2307,31 +2384,31 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2339,31 +2416,31 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>4</v>
@@ -2371,31 +2448,31 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>4</v>
@@ -2403,31 +2480,31 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -2490,95 +2567,95 @@
     </row>
     <row r="2" ht="112" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2586,31 +2663,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>4</v>
@@ -2618,31 +2695,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2650,31 +2727,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2682,31 +2759,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>4</v>
@@ -2714,31 +2791,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>4</v>
@@ -2746,31 +2823,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>36</v>
+        <v>237</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2778,31 +2855,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2810,31 +2887,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>4</v>
@@ -2842,31 +2919,31 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -2874,31 +2951,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2906,31 +2983,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>4</v>
@@ -2938,31 +3015,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>36</v>
+        <v>278</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2970,31 +3047,31 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>4</v>
@@ -3002,31 +3079,31 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3034,31 +3111,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>36</v>
+        <v>278</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3066,31 +3143,31 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>4</v>
@@ -3098,31 +3175,31 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>4</v>
@@ -3130,31 +3207,31 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>4</v>
@@ -3162,31 +3239,31 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>4</v>
@@ -3194,31 +3271,31 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>36</v>
+        <v>278</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3226,31 +3303,31 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>4</v>
@@ -3258,31 +3335,31 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>4</v>
@@ -3290,31 +3367,31 @@
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>4</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="324">
   <si>
     <t>FEATURE</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-26 22:00:46</t>
+    <t>2026-06-28 11:23:59</t>
   </si>
   <si>
     <t>PASS</t>
@@ -63,6 +63,12 @@
     <t>SignUp-001</t>
   </si>
   <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -108,202 +114,181 @@
     <t>Sign in with valid credentials and land on /select-location</t>
   </si>
   <si>
-    <t>Browser open at https://moontower.aiimone.com/Login; user account 'developers@moontower.com' exists; Email field, Password field and Sign In button are visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://moontower.aiimone.com/Login
+    <t>Browser open at /Login; user account 'developers@moontower.com' exists; Email + Password fields and Sign In button visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /Login
 2. Enter 'developers@moontower.com' into the Email field
 3. Enter '12345678' into the Password field
-4. Click the 'Sign In' button</t>
+4. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: developers@moontower.com
 Password: 12345678</t>
   </si>
   <si>
-    <t>Page redirects to /select-location; 'Select Your Location' heading is visible; 'Restaurant: &lt;name&gt;' paragraph confirms the account context</t>
-  </si>
-  <si>
-    <t>User is authenticated; session cookie is set; user is on the location-picker screen</t>
-  </si>
-  <si>
-    <t>Passed in 4.9s on chromium.</t>
+    <t>Redirect to /select-location with 'Select Your Location' heading and 'Restaurant: …' paragraph</t>
+  </si>
+  <si>
+    <t>User authenticated; session cookie set</t>
+  </si>
+  <si>
+    <t>Passed in 4.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (wrong password)</t>
-  </si>
-  <si>
-    <t>Sign in with a valid email but an incorrect password</t>
-  </si>
-  <si>
-    <t>Browser open at /Login; valid email 'developers@moontower.com' exists in the system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Enter 'developers@moontower.com' into the Email field
-3. Enter a deliberately wrong password (e.g., 'WrongPass!2025') into the Password field
-4. Click 'Sign In'</t>
+    <t>AC1: NEGATIVE — wrong password</t>
+  </si>
+  <si>
+    <t>Sign in with valid email but wrong password</t>
+  </si>
+  <si>
+    <t>Browser open at /Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'developers@moontower.com' in Email
+2. Enter a deliberately wrong password
+3. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: developers@moontower.com
 Password: WrongPassword!2025</t>
   </si>
   <si>
-    <t>Auth API returns non-2xx (401); URL stays on /login; no redirect to /select-location</t>
-  </si>
-  <si>
-    <t>User is NOT authenticated; no session cookie set</t>
-  </si>
-  <si>
-    <t>Passed in 7.2s on chromium.</t>
+    <t>Auth API returns non-2xx; URL stays on /login</t>
+  </si>
+  <si>
+    <t>User NOT authenticated</t>
+  </si>
+  <si>
+    <t>Passed in 4.6s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (non-existent email)</t>
-  </si>
-  <si>
-    <t>Sign in with an email that doesn't exist in the system</t>
-  </si>
-  <si>
-    <t>Browser open at /Login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Enter a fresh, unregistered email (e.g., no-such-user-&lt;timestamp&gt;@example.com)
-3. Enter any password
-4. Click 'Sign In'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email: no-such-user-&lt;timestamp&gt;@example.com
+    <t>AC1: NEGATIVE — non-existent email</t>
+  </si>
+  <si>
+    <t>Sign in with an email that doesn't exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a fresh unregistered email
+2. Enter any password
+3. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: no-such-user-&lt;ts&gt;@example.com
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Auth API returns non-2xx; URL stays on /login</t>
-  </si>
-  <si>
-    <t>User is NOT authenticated</t>
-  </si>
-  <si>
-    <t>Passed in 9.8s on chromium.</t>
+    <t>Passed in 4.2s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (empty email)</t>
-  </si>
-  <si>
-    <t>Submit form with the Email field left empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Leave the Email field blank
-3. Enter a password
-4. Click 'Sign In'</t>
+    <t>AC1: NEGATIVE — empty email</t>
+  </si>
+  <si>
+    <t>Submit with the Email field empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave Email blank
+2. Enter a password
+3. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: (empty)
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Form does not navigate to /select-location; user remains on /Login</t>
-  </si>
-  <si>
-    <t>User remains on /Login; no authentication</t>
-  </si>
-  <si>
-    <t>Passed in 5.7s on chromium.</t>
+    <t>Form does not navigate to /select-location</t>
+  </si>
+  <si>
+    <t>User remains on /Login</t>
+  </si>
+  <si>
+    <t>Passed in 13.4s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (empty password)</t>
-  </si>
-  <si>
-    <t>Submit form with the Password field left empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Enter a valid email
-3. Leave the Password field blank
-4. Click 'Sign In'</t>
+    <t>AC1: NEGATIVE — empty password</t>
+  </si>
+  <si>
+    <t>Submit with the Password field empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a valid email
+2. Leave Password blank
+3. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: developers@moontower.com
 Password: (empty)</t>
   </si>
   <si>
-    <t>User remains on /Login</t>
-  </si>
-  <si>
-    <t>Passed in 6.8s on chromium.</t>
+    <t>Passed in 16.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (both fields empty)</t>
-  </si>
-  <si>
-    <t>Submit form with both Email and Password fields empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Leave both fields blank
-3. Click 'Sign In'</t>
+    <t>AC1: NEGATIVE — both fields empty</t>
+  </si>
+  <si>
+    <t>Submit with both Email and Password empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave both fields blank
+2. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: (empty)
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 6.0s on chromium.</t>
+    <t>Passed in 13.2s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (invalid email format, no @)</t>
-  </si>
-  <si>
-    <t>Submit form with an email that doesn't contain '@'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Enter 'developersmoontower.com' (missing @) in Email
-3. Enter any password
-4. Click 'Sign In'</t>
+    <t>AC1: NEGATIVE — invalid email format (no @)</t>
+  </si>
+  <si>
+    <t>Email without '@' is flagged as invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'developersmoontower.com' in Email
+2. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: developersmoontower.com
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Email field reports HTML5 typeMismatch validity; form does not navigate to /select-location</t>
-  </si>
-  <si>
-    <t>Passed in 3.8s on chromium.</t>
+    <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
+  </si>
+  <si>
+    <t>Passed in 17.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
-    <t>AC1: Visit site and try to login — NEGATIVE (invalid email format, missing domain)</t>
-  </si>
-  <si>
-    <t>Submit form with an email missing the domain part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Enter 'developers@' into the Email field
-3. Enter any password
-4. Click 'Sign In'</t>
+    <t>AC1: NEGATIVE — invalid email format (missing domain)</t>
+  </si>
+  <si>
+    <t>Email missing the domain part is flagged as invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'developers@' in Email
+2. Click 'Sign In'</t>
   </si>
   <si>
     <t xml:space="preserve">Email: developers@
@@ -319,140 +304,136 @@
     <t>Password field masks the input by default (type='password')</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Inspect the Password input element</t>
+    <t>1. Inspect the Password input</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
-    <t>Password input has attribute type='password'; characters are rendered as masked dots</t>
-  </si>
-  <si>
-    <t>Passed in 4.8s on chromium.</t>
+    <t>Password input has attribute type='password'</t>
+  </si>
+  <si>
+    <t>Passed in 3.6s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
   </si>
   <si>
-    <t>'Show password' button toggles input type between password and text</t>
-  </si>
-  <si>
-    <t>Browser open at /Login; password field has text in it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type a password into the Password field
-2. Click the 'Show password' button (eye icon)
-3. Click again to re-mask</t>
+    <t>'Show password' toggles between password and text</t>
+  </si>
+  <si>
+    <t>Browser open at /Login; password field has text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Type a password
+2. Click 'Show password'
+3. Click again</t>
   </si>
   <si>
     <t>Password: Secret!2025</t>
   </si>
   <si>
-    <t>Click 1: input type switches to 'text'; click 2: type switches back to 'password'</t>
+    <t>Click 1: type='text'; click 2: type='password'</t>
+  </si>
+  <si>
+    <t>Passed in 3.5s on chromium.</t>
+  </si>
+  <si>
+    <t>Login-UI-03</t>
+  </si>
+  <si>
+    <t>Enter in Password field submits the form</t>
+  </si>
+  <si>
+    <t>Valid credentials filled in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill Email + Password with valid values
+2. Press Enter while focus is on Password</t>
+  </si>
+  <si>
+    <t>Redirect to /select-location</t>
+  </si>
+  <si>
+    <t>User signed in</t>
+  </si>
+  <si>
+    <t>Passed in 6.1s on chromium.</t>
+  </si>
+  <si>
+    <t>Login-UI-04</t>
+  </si>
+  <si>
+    <t>Login form keyboard accessibility</t>
+  </si>
+  <si>
+    <t>Tab order: Email → Password → 'Show password' → 'Forgot password?' → Sign In</t>
+  </si>
+  <si>
+    <t>1. Tab from Email through all interactive elements</t>
+  </si>
+  <si>
+    <t>Focus moves predictably; no element skipped</t>
+  </si>
+  <si>
+    <t>Manual test case — execute per the TEST STEPS column.</t>
+  </si>
+  <si>
+    <t>Login-NAV-01</t>
+  </si>
+  <si>
+    <t>Login navigation</t>
+  </si>
+  <si>
+    <t>'Forgot password?' link navigates to /forgot-password</t>
+  </si>
+  <si>
+    <t>1. Click 'Forgot password?' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to /forgot-password</t>
+  </si>
+  <si>
+    <t>User on the forgot-password screen</t>
+  </si>
+  <si>
+    <t>Passed in 5.0s on chromium.</t>
+  </si>
+  <si>
+    <t>Login-NAV-02</t>
+  </si>
+  <si>
+    <t>'Sign up' link navigates to /signup</t>
+  </si>
+  <si>
+    <t>1. Click 'Sign up' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to /signup</t>
+  </si>
+  <si>
+    <t>User on the signup screen</t>
   </si>
   <si>
     <t>Passed in 3.0s on chromium.</t>
   </si>
   <si>
-    <t>Login-UI-03</t>
-  </si>
-  <si>
-    <t>Pressing Enter inside the Password field submits the form (equivalent to clicking Sign In)</t>
-  </si>
-  <si>
-    <t>Browser open at /Login with valid credentials filled in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill Email with valid value
-2. Fill Password with valid value
-3. Press Enter key while focus is on the Password field</t>
-  </si>
-  <si>
-    <t>Form submits; on success, user is redirected to /select-location</t>
-  </si>
-  <si>
-    <t>User is signed in</t>
-  </si>
-  <si>
-    <t>Passed in 5.8s on chromium.</t>
-  </si>
-  <si>
-    <t>Login-UI-04</t>
-  </si>
-  <si>
-    <t>Login form keyboard accessibility</t>
-  </si>
-  <si>
-    <t>Tab order: Email → Password → 'Show password' → 'Forgot password?' → Sign In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Click into the Email field (or press Tab from the address bar)
-3. Press Tab repeatedly and observe which element receives focus</t>
-  </si>
-  <si>
-    <t>Focus moves predictably through Email → Password → Show-password → Forgot link → Sign In; no element is skipped or unreachable via keyboard</t>
-  </si>
-  <si>
-    <t>Manual test case — execute per the TEST STEPS column.</t>
-  </si>
-  <si>
-    <t>Login-NAV-01</t>
-  </si>
-  <si>
-    <t>Login page navigation links</t>
-  </si>
-  <si>
-    <t>'Forgot password?' link navigates to /forgot-password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Click the 'Forgot password?' link</t>
-  </si>
-  <si>
-    <t>Link's href is '/forgot-password'; browser navigates to https://moontower.aiimone.com/forgot-password</t>
-  </si>
-  <si>
-    <t>User on the forgot-password screen</t>
-  </si>
-  <si>
-    <t>Passed in 5.6s on chromium.</t>
-  </si>
-  <si>
-    <t>Login-NAV-02</t>
-  </si>
-  <si>
-    <t>'Sign up' link navigates to /signup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Click the 'Sign up' link</t>
-  </si>
-  <si>
-    <t>Link's href is '/signup'; browser navigates to https://moontower.aiimone.com/signup</t>
-  </si>
-  <si>
-    <t>User on the signup screen</t>
-  </si>
-  <si>
     <t>Login-NAV-03</t>
   </si>
   <si>
-    <t>'← Back' link navigates to the homepage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Click the '← Back' link</t>
-  </si>
-  <si>
-    <t>Link's href is '/'; browser navigates to the homepage</t>
-  </si>
-  <si>
-    <t>User on the homepage</t>
-  </si>
-  <si>
-    <t>Passed in 5.2s on chromium.</t>
+    <t>'← Back' link navigates to homepage</t>
+  </si>
+  <si>
+    <t>1. Click '← Back' link</t>
+  </si>
+  <si>
+    <t>Browser navigates to /</t>
+  </si>
+  <si>
+    <t>User on homepage</t>
+  </si>
+  <si>
+    <t>Passed in 3.2s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -461,11 +442,11 @@
     <t>Login edge cases</t>
   </si>
   <si>
-    <t>Login with leading/trailing whitespace in the email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter '  developers@moontower.com  ' (with spaces) in Email
-2. Enter the valid password
+    <t>Whitespace in email is trimmed (or rejected with clear validation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter '  developers@moontower.com  ' in Email
+2. Enter valid password
 3. Click Sign In</t>
   </si>
   <si>
@@ -473,7 +454,7 @@
 Password: 12345678</t>
   </si>
   <si>
-    <t>App SHOULD trim whitespace and authenticate successfully — OR show a clear validation error. Either is acceptable; silent failure is not.</t>
+    <t>App trims and authenticates OR clearly rejects</t>
   </si>
   <si>
     <t>Login-EDGE-02</t>
@@ -483,7 +464,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Enter 'DEVELOPERS@MOONTOWER.COM' in Email
-2. Enter the valid password
+2. Enter valid password
 3. Click Sign In</t>
   </si>
   <si>
@@ -491,25 +472,24 @@
 Password: 12345678</t>
   </si>
   <si>
-    <t>App should authenticate successfully (email addresses are case-insensitive)</t>
+    <t>Email is case-insensitive; auth succeeds</t>
   </si>
   <si>
     <t>Login-EDGE-03</t>
   </si>
   <si>
-    <t>Login with very long email (256+ characters)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Generate an email of 260 characters total
-2. Paste into Email field
-3. Enter any password and click Sign In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email: &lt;250 random chars&gt;@x.co
+    <t>Login with very long email (256+ chars)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Generate a 260-char email
+2. Paste into Email; click Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: &lt;250 chars&gt;@x.co
 Password: 12345678</t>
   </si>
   <si>
-    <t>Validation rejects the email as invalid (RFC 5321 limit is 254 chars total); no 500 error</t>
+    <t>Validation rejects per RFC 5321; no 500</t>
   </si>
   <si>
     <t>Login-SEC-01</t>
@@ -518,139 +498,123 @@
     <t>Login security</t>
   </si>
   <si>
-    <t>Password input element has type='password' (not visible in DOM as plaintext)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to /Login
-2. Open DevTools → Elements
-3. Inspect the password input</t>
-  </si>
-  <si>
-    <t>The input has the attribute type='password'; the typed value is masked in the visible DOM</t>
+    <t>Password input has type='password' (masked in DOM)</t>
+  </si>
+  <si>
+    <t>1. Inspect the password input in DevTools</t>
+  </si>
+  <si>
+    <t>input has attribute type='password'</t>
   </si>
   <si>
     <t>Login-SEC-02</t>
   </si>
   <si>
-    <t>Credentials are not appended to the URL after submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill valid credentials and click Sign In
-2. Inspect the address bar after submission and during the redirect</t>
-  </si>
-  <si>
-    <t>URL never contains email or password as query parameters (form must POST, not GET); no credential traces in browser history</t>
-  </si>
-  <si>
-    <t>Credentials not exposed via URL</t>
+    <t>Credentials are not appended to URL after submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Submit valid credentials
+2. Inspect URL during/after the redirect</t>
+  </si>
+  <si>
+    <t>URL never carries credentials (form must POST, not GET)</t>
+  </si>
+  <si>
+    <t>Credentials not exposed</t>
   </si>
   <si>
     <t>Login-SEC-03</t>
   </si>
   <si>
-    <t>SQL-injection-style payload in Email field is handled safely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter "admin' OR '1'='1" in the Email field
-2. Enter any password
-3. Click Sign In</t>
+    <t>SQL-injection payload in Email field is handled safely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter "admin' OR '1'='1" in Email
+2. Click Sign In</t>
   </si>
   <si>
     <t xml:space="preserve">Email: admin' OR '1'='1
 Password: anything</t>
   </si>
   <si>
-    <t>The app treats the input as a string; either email validator rejects it OR auth API rejects with 'Invalid credentials'. No DB error surfaces; no successful login.</t>
-  </si>
-  <si>
-    <t>User remains on /Login; no DB compromise</t>
+    <t>Email validator rejects OR auth API rejects with 'Invalid credentials'; no DB error</t>
   </si>
   <si>
     <t>Login-SEC-04</t>
   </si>
   <si>
-    <t>Rate limiting / account lockout after multiple failed attempts</t>
-  </si>
-  <si>
-    <t>Browser open at /Login; valid email known</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit wrong-password attempt for the same email N times in quick succession (e.g., 5–10 times)
-2. Observe whether subsequent attempts are throttled or locked out</t>
+    <t>Rate limiting / lockout after N failed attempts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Submit wrong password 5–10 times for the same email
+2. Observe if subsequent attempts are throttled or locked</t>
   </si>
   <si>
     <t xml:space="preserve">Email: developers@moontower.com
-Password: &lt;wrong password attempts&gt;</t>
-  </si>
-  <si>
-    <t>After a threshold of failed attempts, the system rate-limits (HTTP 429) or locks the account temporarily. Indefinite unlimited attempts are a security gap.</t>
-  </si>
-  <si>
-    <t>Account is throttled or locked</t>
+Password: &lt;wrong&gt;</t>
+  </si>
+  <si>
+    <t>After a threshold, system rate-limits (429) or locks the account</t>
+  </si>
+  <si>
+    <t>Account throttled or locked</t>
   </si>
   <si>
     <t>SignUp-001-AC1-POS-01</t>
   </si>
   <si>
-    <t>AC1: Fill signup form and register — POSITIVE (happy path)</t>
+    <t>AC1: Fill signup form and register — POSITIVE (DESTRUCTIVE)</t>
   </si>
   <si>
     <t>Complete the 2-step signup with valid data; server accepts the registration</t>
   </si>
   <si>
-    <t>Browser open at /signup; step-1 'Register Your Restaurant' form is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill Restaurant Name with a unique timestamp-suffixed value
-2. Verify Subdomain auto-populates (read-only)
-3. Fill Full Name, Business Email, Phone Number with valid values
-4. Click 'Next' → step-2 'Set Password' appears
-5. Fill Password and Confirm Password (matching)
-6. Check 'I agree to the Terms and Conditions'
-7. Click 'Create Account'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant: MoonTest&lt;ts&gt;
-Email: arslan.moon+ac1&lt;ts&gt;@yopmail.com
+    <t>RUN_DESTRUCTIVE_SIGNUP=1; step-1 form visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all step-1 required fields with valid data
+2. Click Next
+3. Fill matching passwords + accept Terms
+4. Click Create Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant: MoonGherkinDestr&lt;ts&gt;
+Email: arslan.moon+destr-&lt;ts&gt;@yopmail.com
 Password: TestPass!2025</t>
   </si>
   <si>
-    <t>Server accepts registration; URL leaves /signup</t>
-  </si>
-  <si>
-    <t>New tenant created; user proceeds to /select-location</t>
-  </si>
-  <si>
-    <t>Skipped.</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>URL leaves /signup; server accepted the registration</t>
+  </si>
+  <si>
+    <t>New tenant created</t>
+  </si>
+  <si>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>SignUp-001-AC2-POS-01</t>
   </si>
   <si>
-    <t>AC2: Verify the user is registered — POSITIVE</t>
-  </si>
-  <si>
-    <t>After Create Account, three independent post-registration signals all hold</t>
-  </si>
-  <si>
-    <t>Browser open at /signup; valid registration just submitted</t>
+    <t>AC2: Verify the user is registered — POSITIVE (DESTRUCTIVE)</t>
+  </si>
+  <si>
+    <t>After Create Account, three independent post-registration signals hold</t>
+  </si>
+  <si>
+    <t>RUN_DESTRUCTIVE_SIGNUP=1; valid registration just submitted</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete the full 2-step signup with valid data
-2. Verify URL equals /select-location
-3. Verify 'Select Your Location' heading is visible
-4. Verify 'Restaurant: &lt;name&gt;' paragraph references the just-created restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant: MoonVerify&lt;ts&gt;
-Email: arslan.moon+ac2&lt;ts&gt;@yopmail.com
-Password: TestPass!2025</t>
-  </si>
-  <si>
-    <t>All three signals visible simultaneously</t>
+2. Verify URL = /select-location
+3. Verify 'Select Your Location' heading visible
+4. Verify the 'Restaurant: &lt;name&gt;' paragraph references the new restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant: MoonGherkinDestr&lt;ts&gt;
+Email: arslan.moon+destr-&lt;ts&gt;@yopmail.com</t>
+  </si>
+  <si>
+    <t>All three signals hold simultaneously</t>
   </si>
   <si>
     <t>Registration confirmed end-to-end</t>
@@ -659,90 +623,78 @@
     <t>SignUp-001-NEG-01</t>
   </si>
   <si>
-    <t>Step 1 validation — required field missing</t>
+    <t>Step 1 validation — required field missing (Restaurant Name)</t>
   </si>
   <si>
     <t>Submit step 1 with Restaurant Name empty</t>
   </si>
   <si>
-    <t>Browser open at /signup; step-1 form visible</t>
+    <t>Browser open at /signup</t>
   </si>
   <si>
     <t xml:space="preserve">1. Leave Restaurant Name empty
-2. Fill all other required step-1 fields with valid values
-3. Click 'Next'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant Name: (empty)
-Email: arslan.moon+rn&lt;ts&gt;@yopmail.com</t>
-  </si>
-  <si>
-    <t>Form does not advance; step-1 heading 'Register Your Restaurant' still visible; step-2 heading 'Set Password' is NOT visible</t>
+2. Fill all other required step-1 fields
+3. Click Next</t>
+  </si>
+  <si>
+    <t>Restaurant Name: (empty)</t>
+  </si>
+  <si>
+    <t>Form does not advance; step-1 heading still visible</t>
   </si>
   <si>
     <t>User remains on step 1</t>
   </si>
   <si>
-    <t>Passed in 3.7s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-02</t>
   </si>
   <si>
+    <t>Step 1 validation — required field missing (Full Name)</t>
+  </si>
+  <si>
     <t>Submit step 1 with Full Name empty</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Fill Restaurant Name; leave Full Name empty
-2. Fill remaining required fields
-3. Click 'Next'</t>
+    <t xml:space="preserve">1. Fill all step-1 fields except Full Name
+2. Click Next</t>
   </si>
   <si>
     <t>Full Name: (empty)</t>
   </si>
   <si>
-    <t>Form does not advance; step-1 heading still visible</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-03</t>
   </si>
   <si>
+    <t>Step 1 validation — required field missing (Business Email)</t>
+  </si>
+  <si>
     <t>Submit step 1 with Business Email empty</t>
   </si>
   <si>
     <t xml:space="preserve">1. Fill all step-1 fields except Business Email
-2. Click 'Next'</t>
+2. Click Next</t>
   </si>
   <si>
     <t>Business Email: (empty)</t>
   </si>
   <si>
-    <t>Passed in 3.4s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
     <t>Step 1 validation — invalid email format</t>
   </si>
   <si>
-    <t>Submit step 1 with a Business Email that has no '@' symbol</t>
-  </si>
-  <si>
-    <t>Browser open at /signup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all step-1 fields
-2. In Business Email enter 'arslan-yopmail.com' (no @)
-3. Click 'Next'</t>
+    <t>Submit with Business Email missing '@'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In Business Email enter 'arslan-yopmail.com' (no @)
+2. Click Next</t>
   </si>
   <si>
     <t>Business Email: arslan-yopmail.com</t>
   </si>
   <si>
-    <t>input[type=email] reports typeMismatch validity; form does not advance</t>
-  </si>
-  <si>
-    <t>Passed in 5.9s on chromium.</t>
+    <t>Email field reports HTML5 typeMismatch; form does not advance</t>
   </si>
   <si>
     <t>SignUp-001-NEG-05</t>
@@ -751,18 +703,17 @@
     <t>Step 1 validation — invalid phone format</t>
   </si>
   <si>
-    <t>Submit step 1 with letters in the Phone Number field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all step-1 fields
-2. In Phone Number enter 'abc1234567'
-3. Click 'Next'</t>
+    <t>Submit step 1 with letters in Phone Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In Phone Number enter 'abc1234567'
+2. Click Next</t>
   </si>
   <si>
     <t>Phone Number: abc1234567</t>
   </si>
   <si>
-    <t>Validation message rejects the input OR the field strips non-digits; form does not advance if invalid</t>
+    <t>Validation rejects or input strips non-digits</t>
   </si>
   <si>
     <t>SignUp-001-NEG-06</t>
@@ -771,21 +722,21 @@
     <t>Step 1 — email uniqueness (server-side)</t>
   </si>
   <si>
-    <t>Submit step 1 with an email already registered in the system</t>
-  </si>
-  <si>
-    <t>An account already exists for 'arslan.moon@yopmail.com'</t>
+    <t>Submit step 1 with an email already registered</t>
+  </si>
+  <si>
+    <t>An account exists for 'arslan.moon@yopmail.com'</t>
   </si>
   <si>
     <t xml:space="preserve">1. Fill all step-1 fields using the already-registered email
-2. Click Next (may reach step 2)
-3. Complete step 2 if reached and click Create Account</t>
+2. Click Next; complete step 2 if reached
+3. Click Create Account</t>
   </si>
   <si>
     <t>Business Email: arslan.moon@yopmail.com</t>
   </si>
   <si>
-    <t>Server rejects with 'Email already in use' or similar; URL stays on /signup; no new tenant created</t>
+    <t>Server rejects with 'Email already in use'</t>
   </si>
   <si>
     <t>No duplicate account</t>
@@ -797,10 +748,10 @@
     <t>Step 1 — Subdomain auto-population</t>
   </si>
   <si>
-    <t>Subdomain is read-only and auto-derived from Restaurant Name (lowercased, kebab-cased)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect the Subdomain input; confirm it has the readonly attribute
+    <t>Subdomain is read-only and auto-derives (kebab-cased) from Restaurant Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Inspect Subdomain; confirm readonly attribute
 2. Type 'My Eatery 42' into Restaurant Name
 3. Read the Subdomain value</t>
   </si>
@@ -808,10 +759,7 @@
     <t>Restaurant Name: My Eatery 42</t>
   </si>
   <si>
-    <t>Subdomain matches /^[a-z0-9-]+$/ and contains 'my' and 'eatery' (e.g., 'my-eatery-42'); the field has the readonly attribute</t>
-  </si>
-  <si>
-    <t>Passed in 4.3s on chromium.</t>
+    <t>Subdomain ∈ /^[a-z0-9-]+$/; contains 'my' + 'eatery'</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -820,23 +768,23 @@
     <t>Step 2 — password validation (mismatch)</t>
   </si>
   <si>
-    <t>Step 2 does NOT submit when Password and Confirm Password differ</t>
-  </si>
-  <si>
-    <t>Step 2 'Set Password' visible (step 1 completed)</t>
+    <t>Mismatching passwords prevent submission</t>
+  </si>
+  <si>
+    <t>Step 2 visible</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter 'TestPass!2025' in Password
 2. Enter 'DifferentTestPass!2025' in Confirm Password
-3. Check the Terms checkbox
-4. Attempt to click 'Create Account'</t>
+3. Check Terms
+4. Click Create Account</t>
   </si>
   <si>
     <t xml:space="preserve">Password: TestPass!2025
 Confirm Password: DifferentTestPass!2025</t>
   </si>
   <si>
-    <t>Form does not submit; URL stays on /signup; step-2 heading still visible</t>
+    <t>URL stays on /signup; step-2 heading still visible</t>
   </si>
   <si>
     <t>User remains on step 2</t>
@@ -845,24 +793,20 @@
     <t>SignUp-001-NEG-09</t>
   </si>
   <si>
-    <t>Step 2 — password validation (too short)</t>
+    <t>Step 2 — password too short</t>
   </si>
   <si>
     <t>Step 2 enforces a minimum password length</t>
   </si>
   <si>
-    <t>Step 2 visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter a short password (e.g., 'abc') in both Password and Confirm Password
-2. Check Terms
-3. Attempt Create Account</t>
+    <t xml:space="preserve">1. Enter a short password (e.g., 'abc') in both fields
+2. Check Terms; attempt Create Account</t>
   </si>
   <si>
     <t>Password: abc</t>
   </si>
   <si>
-    <t>Validation message: minimum-length requirement is not met; submission is blocked</t>
+    <t>Validation: minimum-length not met; submission blocked</t>
   </si>
   <si>
     <t>SignUp-001-NEG-10</t>
@@ -871,24 +815,21 @@
     <t>Step 2 — terms checkbox required</t>
   </si>
   <si>
-    <t>Create Account is disabled until 'I agree to the Terms and Conditions' is checked</t>
-  </si>
-  <si>
-    <t>Step 2 visible; passwords filled with matching valid values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill Password and Confirm Password with valid matching values
-2. Leave the Terms checkbox UNCHECKED
-3. Inspect the Create Account button state</t>
-  </si>
-  <si>
-    <t>Terms checkbox: unchecked</t>
-  </si>
-  <si>
-    <t>Create Account button is disabled (cannot be clicked); Terms checkbox is unchecked</t>
-  </si>
-  <si>
-    <t>Passed in 4.4s on chromium.</t>
+    <t>Create Account is disabled until Terms is checked</t>
+  </si>
+  <si>
+    <t>Step 2 visible; passwords filled (matching)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill Password + Confirm with matching values
+2. Leave Terms UNCHECKED
+3. Inspect Create Account button</t>
+  </si>
+  <si>
+    <t>Terms: unchecked</t>
+  </si>
+  <si>
+    <t>Create Account button is disabled</t>
   </si>
   <si>
     <t>SignUp-001-UI-01</t>
@@ -897,17 +838,13 @@
     <t>Step 1 — read-only fields</t>
   </si>
   <si>
-    <t>Subdomain, Location Name, and Address fields are read-only and cannot be edited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect each of #subDomain, #locationName, #locationAddress
-2. Confirm each has the readonly attribute</t>
-  </si>
-  <si>
-    <t>All three inputs have the readonly attribute set; values cannot be edited by typing</t>
-  </si>
-  <si>
-    <t>Passed in 3.6s on chromium.</t>
+    <t>Subdomain, Location Name, Address fields are read-only</t>
+  </si>
+  <si>
+    <t>1. Inspect each of #subDomain, #locationName, #locationAddress</t>
+  </si>
+  <si>
+    <t>All three have the readonly attribute</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -916,18 +853,18 @@
     <t>Step 1/2 — Next button gating</t>
   </si>
   <si>
-    <t>Next button reflects validity of step-1 required fields in real time</t>
-  </si>
-  <si>
-    <t>Browser open at /signup; form is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Observe the Next button state when the form is empty
-2. Progressively fill each required field
-3. Observe the Next button state at each step</t>
-  </si>
-  <si>
-    <t>Next button is disabled when any required field is empty/invalid; becomes enabled once all required fields have valid values</t>
+    <t>Next reflects validity of step-1 required fields in real time</t>
+  </si>
+  <si>
+    <t>Form empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Observe Next state when empty
+2. Fill each required field progressively
+3. Observe Next state at each step</t>
+  </si>
+  <si>
+    <t>Next is disabled when any required field is empty; enables once all valid</t>
   </si>
   <si>
     <t>SignUp-001-UI-03</t>
@@ -940,68 +877,53 @@
   </si>
   <si>
     <t xml:space="preserve">1. Type into Password
-2. Click the 'Show password' button
+2. Click 'Show password'
 3. Click again to re-mask</t>
   </si>
   <si>
-    <t>First click: type becomes 'text'; second click: type returns to 'password'</t>
-  </si>
-  <si>
-    <t>Passed in 4.1s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-UI-04</t>
   </si>
   <si>
-    <t>Step 2 — Back button preserves step-1 data</t>
-  </si>
-  <si>
-    <t>Clicking Back from step 2 returns to step 1 with the previously entered values intact</t>
-  </si>
-  <si>
-    <t>Step 1 was filled and Next clicked; user is on step 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. On step 2, click 'Back'
+    <t>Step 2 — Back preserves step-1 data</t>
+  </si>
+  <si>
+    <t>Clicking Back returns to step 1 with values intact</t>
+  </si>
+  <si>
+    <t>Step 2 visible after Step 1 fill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On step 2, click Back
 2. Inspect each step-1 field</t>
   </si>
   <si>
-    <t>Step 1 reappears; all editable fields retain previously entered values</t>
-  </si>
-  <si>
-    <t>User can navigate back and forth without losing input</t>
+    <t>Step 1 reappears with all editable values intact</t>
+  </si>
+  <si>
+    <t>No data loss</t>
   </si>
   <si>
     <t>SignUp-001-NAV-01</t>
   </si>
   <si>
-    <t>Signup page navigation</t>
-  </si>
-  <si>
-    <t>'Sign in' link on /signup navigates to /login</t>
-  </si>
-  <si>
-    <t>1. Click the 'Sign in' link below the form</t>
-  </si>
-  <si>
-    <t>Link href ends with /login; browser navigates to /login</t>
+    <t>Signup navigation</t>
+  </si>
+  <si>
+    <t>'Sign in' link navigates to /login</t>
+  </si>
+  <si>
+    <t>1. Click 'Sign in' link</t>
+  </si>
+  <si>
+    <t>URL ends with /login</t>
   </si>
   <si>
     <t>User on the login screen</t>
   </si>
   <si>
-    <t>Passed in 2.8s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NAV-02</t>
   </si>
   <si>
-    <t>1. Click the '← Back' link</t>
-  </si>
-  <si>
-    <t>Link href is '/'; browser navigates to the homepage</t>
-  </si>
-  <si>
     <t>SignUp-001-EDGE-01</t>
   </si>
   <si>
@@ -1012,14 +934,13 @@
   </si>
   <si>
     <t xml:space="preserve">1. Enter '   My Eatery   ' in Restaurant Name
-2. Observe the Subdomain auto-fill
-3. Complete the rest of step 1 and proceed</t>
+2. Observe Subdomain auto-fill</t>
   </si>
   <si>
     <t>Restaurant Name: '   My Eatery   '</t>
   </si>
   <si>
-    <t>App trims whitespace before deriving the subdomain</t>
+    <t>App trims whitespace; subdomain reflects the trimmed name</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-02</t>
@@ -1029,19 +950,19 @@
   </si>
   <si>
     <t xml:space="preserve">1. Enter 'My Eatery &amp; Café (2026)!' in Restaurant Name
-2. Observe Subdomain auto-fill</t>
+2. Observe Subdomain</t>
   </si>
   <si>
     <t>Restaurant Name: My Eatery &amp; Café (2026)!</t>
   </si>
   <si>
-    <t>Subdomain is derived to a URL-safe slug; no special characters leak</t>
+    <t>Subdomain is URL-safe slug only</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-03</t>
   </si>
   <si>
-    <t>Disposable email (yopmail) is accepted (or rejected with clear message)</t>
+    <t>Disposable email (yopmail) accepted or rejected with clear message</t>
   </si>
   <si>
     <t xml:space="preserve">1. Use a yopmail address
@@ -1051,26 +972,26 @@
     <t>Email: arslan.moon+test&lt;ts&gt;@yopmail.com</t>
   </si>
   <si>
-    <t>App either accepts the email and proceeds, or explicitly rejects with a clear message</t>
+    <t>Either accepted or explicitly rejected</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-04</t>
   </si>
   <si>
-    <t>Subdomain collision — Restaurant Name yields a subdomain that already exists</t>
-  </si>
-  <si>
-    <t>An account 'demo' already exists; new user tries Restaurant Name 'Demo'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter 'Demo' as Restaurant Name (collides with existing tenant)
-2. Complete the form and click Create Account</t>
+    <t>Subdomain collision with existing tenant</t>
+  </si>
+  <si>
+    <t>Tenant 'demo' already exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'Demo' as Restaurant Name (auto-derives to 'demo')
+2. Complete form; click Create Account</t>
   </si>
   <si>
     <t>Restaurant Name: Demo</t>
   </si>
   <si>
-    <t>Server rejects with 'Subdomain already in use' or similar</t>
+    <t>Server rejects: 'Subdomain already in use'</t>
   </si>
   <si>
     <t>No duplicate tenant</t>
@@ -1085,25 +1006,24 @@
     <t>Password fields use type='password' (masked in DOM)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Inspect Password and Confirm Password inputs
-2. Confirm initial type attribute</t>
-  </si>
-  <si>
-    <t>Both inputs default to type='password'</t>
+    <t>1. Inspect Password and Confirm Password</t>
+  </si>
+  <si>
+    <t>Both default to type='password'</t>
   </si>
   <si>
     <t>SignUp-001-SEC-02</t>
   </si>
   <si>
-    <t>Form posts over HTTPS (credentials encrypted in transit)</t>
+    <t>Form posts over HTTPS</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open DevTools → Network
-2. Submit the form
-3. Inspect the request protocol</t>
-  </si>
-  <si>
-    <t>Form submission goes to an https:// endpoint</t>
+2. Submit form
+3. Inspect request protocol</t>
+  </si>
+  <si>
+    <t>Submission goes to an https:// endpoint</t>
   </si>
   <si>
     <t>SignUp-001-SEC-03</t>
@@ -1113,35 +1033,32 @@
   </si>
   <si>
     <t xml:space="preserve">1. Enter '&lt;script&gt;alert(1)&lt;/script&gt;' as Restaurant Name
-2. Complete signup and observe the post-signup screen</t>
+2. Complete signup and observe post-signup screen</t>
   </si>
   <si>
     <t>Restaurant Name: &lt;script&gt;alert(1)&lt;/script&gt;</t>
   </si>
   <si>
-    <t>No alert fires; value is escaped or rejected</t>
-  </si>
-  <si>
-    <t>XSS does not execute</t>
+    <t>No alert; value escaped or rejected</t>
   </si>
   <si>
     <t>SignUp-001-SEC-04</t>
   </si>
   <si>
-    <t>Password not echoed in the response or DOM after successful submission</t>
+    <t>Password not echoed in DOM or response after submit</t>
   </si>
   <si>
     <t>Successful signup just completed</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open DevTools after Create Account succeeds
+    <t xml:space="preserve">1. After Create Account, open DevTools
 2. Search DOM and HTTP responses for the password string</t>
   </si>
   <si>
     <t>Password: TestPass!2025</t>
   </si>
   <si>
-    <t>Password does NOT appear in DOM or any HTTP response body</t>
+    <t>Password not found in DOM or any response body</t>
   </si>
   <si>
     <t>Password not leaked</t>
@@ -1177,18 +1094,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF856404"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF4338CA"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF6C757D"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -1212,17 +1129,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9ECEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1265,10 +1182,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1704,51 +1621,51 @@
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5">
         <v>48</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>28</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>20</v>
       </c>
-      <c r="F4" s="4">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="F4" s="5">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5">
         <v>0</v>
       </c>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1776,191 +1693,191 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1968,95 +1885,95 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2064,31 +1981,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2096,31 +2013,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2128,31 +2045,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2160,63 +2077,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2224,31 +2141,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2256,31 +2173,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2288,127 +2205,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="H20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2416,97 +2333,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2535,865 +2452,865 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" ht="112" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>181</v>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>277</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>295</v>
+        <v>129</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J25" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>333</v>
+        <v>90</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J26" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -51,7 +51,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-28 11:23:59</t>
+    <t>2026-06-28 11:34:24</t>
   </si>
   <si>
     <t>PASS</t>
@@ -133,7 +133,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 4.7s on chromium.</t>
+    <t>Passed in 6.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -163,7 +163,7 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 4.6s on chromium.</t>
+    <t>Passed in 8.3s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -184,7 +184,7 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Passed in 4.2s on chromium.</t>
+    <t>Passed in 5.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -211,7 +211,7 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 13.4s on chromium.</t>
+    <t>Passed in 15.0s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -232,7 +232,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 16.3s on chromium.</t>
+    <t>Passed in 13.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-05</t>
@@ -252,7 +252,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 13.2s on chromium.</t>
+    <t>Passed in 14.4s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -275,7 +275,7 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
-    <t>Passed in 17.0s on chromium.</t>
+    <t>Passed in 15.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -295,6 +295,9 @@
 Password: Whatever!2025</t>
   </si>
   <si>
+    <t>Passed in 15.2s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -313,7 +316,7 @@
     <t>Password input has attribute type='password'</t>
   </si>
   <si>
-    <t>Passed in 3.6s on chromium.</t>
+    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -336,7 +339,7 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
-    <t>Passed in 3.5s on chromium.</t>
+    <t>Passed in 5.1s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-03</t>
@@ -358,7 +361,7 @@
     <t>User signed in</t>
   </si>
   <si>
-    <t>Passed in 6.1s on chromium.</t>
+    <t>Passed in 6.6s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-04</t>
@@ -397,7 +400,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 5.0s on chromium.</t>
+    <t>Passed in 4.5s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -415,7 +418,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
+    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -431,9 +434,6 @@
   </si>
   <si>
     <t>User on homepage</t>
-  </si>
-  <si>
-    <t>Passed in 3.2s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -1973,7 +1973,7 @@
         <v>60</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -1981,31 +1981,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2013,31 +2013,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2045,31 +2045,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2077,31 +2077,31 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>4</v>
@@ -2109,31 +2109,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2141,31 +2141,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2173,31 +2173,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2226,10 +2226,10 @@
         <v>137</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>4</v>
@@ -2258,10 +2258,10 @@
         <v>142</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>4</v>
@@ -2293,7 +2293,7 @@
         <v>60</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>4</v>
@@ -2316,16 +2316,16 @@
         <v>151</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2357,7 +2357,7 @@
         <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>4</v>
@@ -2389,7 +2389,7 @@
         <v>60</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>4</v>
@@ -2421,7 +2421,7 @@
         <v>168</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>4</v>
@@ -2604,7 +2604,7 @@
         <v>193</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>4</v>
@@ -2700,7 +2700,7 @@
         <v>193</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>4</v>
@@ -2732,7 +2732,7 @@
         <v>223</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>4</v>
@@ -2761,7 +2761,7 @@
         <v>229</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>177</v>
@@ -2828,7 +2828,7 @@
         <v>237</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>4</v>
@@ -2883,13 +2883,13 @@
         <v>254</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>255</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>177</v>
@@ -2915,16 +2915,16 @@
         <v>260</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>4</v>
@@ -2947,13 +2947,13 @@
         <v>265</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>177</v>
@@ -2979,7 +2979,7 @@
         <v>270</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>271</v>
@@ -2988,7 +2988,7 @@
         <v>272</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>4</v>
@@ -3011,7 +3011,7 @@
         <v>276</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>277</v>
@@ -3034,22 +3034,22 @@
         <v>274</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>177</v>
@@ -3081,10 +3081,10 @@
         <v>285</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>4</v>
@@ -3113,10 +3113,10 @@
         <v>290</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>4</v>
@@ -3145,10 +3145,10 @@
         <v>295</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>4</v>
@@ -3180,7 +3180,7 @@
         <v>302</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>4</v>
@@ -3203,13 +3203,13 @@
         <v>306</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>307</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>177</v>
@@ -3235,16 +3235,16 @@
         <v>310</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>311</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>4</v>
@@ -3273,10 +3273,10 @@
         <v>316</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>4</v>
@@ -3308,7 +3308,7 @@
         <v>323</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>4</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -7,13 +7,15 @@
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Login" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="SignUp-001" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Dashboard-001" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="DashBoard-002" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="347">
   <si>
     <t>FEATURE</t>
   </si>
@@ -51,10 +53,10 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-06-28 11:34:24</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -63,10 +65,16 @@
     <t>SignUp-001</t>
   </si>
   <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
+    <t>verify-dashboard</t>
+  </si>
+  <si>
+    <t>Dashboard-001</t>
+  </si>
+  <si>
+    <t>verify-dashboard-with-tab</t>
+  </si>
+  <si>
+    <t>DashBoard-002</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -133,7 +141,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 6.3s on chromium.</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -163,9 +171,6 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 8.3s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -184,9 +189,6 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Passed in 5.9s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -211,9 +213,6 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 15.0s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -232,9 +231,6 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 13.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -252,9 +248,6 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 14.4s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
@@ -275,9 +268,6 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
-    <t>Passed in 15.1s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -295,9 +285,6 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 15.2s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -314,9 +301,6 @@
   </si>
   <si>
     <t>Password input has attribute type='password'</t>
-  </si>
-  <si>
-    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -339,9 +323,6 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
-    <t>Passed in 5.1s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -361,9 +342,6 @@
     <t>User signed in</t>
   </si>
   <si>
-    <t>Passed in 6.6s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -400,9 +378,6 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 4.5s on chromium.</t>
-  </si>
-  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -416,9 +391,6 @@
   </si>
   <si>
     <t>User on the signup screen</t>
-  </si>
-  <si>
-    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -589,9 +561,6 @@
     <t>New tenant created</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
-  </si>
-  <si>
     <t>SignUp-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1062,13 +1031,126 @@
   </si>
   <si>
     <t>Password not leaked</t>
+  </si>
+  <si>
+    <t>Dashboard-001-AC1-POS-01</t>
+  </si>
+  <si>
+    <t>AC1: Visit the website and log in with the given credentials</t>
+  </si>
+  <si>
+    <t>Sign in with the provided credentials and land on the location picker</t>
+  </si>
+  <si>
+    <t>Browser open at /login; account 'developers@moontower.com' exists; Email + Password fields and Sign In button visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to https://moontower.aiimone.com/login
+2. Enter 'developers@moontower.com' into the Email field
+3. Enter '12345678' into the Password field
+4. Click 'Sign In'</t>
+  </si>
+  <si>
+    <t>App leaves /login and redirects to /select-location (the location-picker screen)</t>
+  </si>
+  <si>
+    <t>User authenticated; session established</t>
+  </si>
+  <si>
+    <t>Dashboard-001-AC2-POS-01</t>
+  </si>
+  <si>
+    <t>AC2: After login the 'Select Your Location' prompt is shown</t>
+  </si>
+  <si>
+    <t>The 'Select Your Location' heading is visible after a successful login</t>
+  </si>
+  <si>
+    <t>Logged in with valid credentials; on /select-location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in with the provided credentials
+2. Observe the post-login screen</t>
+  </si>
+  <si>
+    <t>The heading 'Select Your Location' is visible</t>
+  </si>
+  <si>
+    <t>User remains on /select-location awaiting a location choice</t>
+  </si>
+  <si>
+    <t>Dashboard-001-AC3-POS-01</t>
+  </si>
+  <si>
+    <t>AC3: Click 'Main Location' and verify the dashboard URL</t>
+  </si>
+  <si>
+    <t>Choosing 'Main Location' routes to the inventory-vendors dashboard</t>
+  </si>
+  <si>
+    <t>Logged in; on /select-location with the 'Main Location' button visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in with the provided credentials
+2. Click the 'Main Location' button
+3. Inspect the resulting URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location: Main Location
+Expected URL: https://moontower.aiimone.com/inventory-vendors</t>
+  </si>
+  <si>
+    <t>URL is exactly https://moontower.aiimone.com/inventory-vendors</t>
+  </si>
+  <si>
+    <t>User is on the inventory-vendors dashboard</t>
+  </si>
+  <si>
+    <t>DashBoard-002-AC1-POS-01</t>
+  </si>
+  <si>
+    <t>DashBoard-002-AC2-POS-01</t>
+  </si>
+  <si>
+    <t>DashBoard-002-AC3-POS-01</t>
+  </si>
+  <si>
+    <t>User is on the inventory-vendors dashboard (Inventory sub-view by default)</t>
+  </si>
+  <si>
+    <t>DashBoard-002-AC4-POS-01</t>
+  </si>
+  <si>
+    <t>AC4: Click on the Inventory tab</t>
+  </si>
+  <si>
+    <t>Clicking the Inventory sidebar tab activates the Inventory view</t>
+  </si>
+  <si>
+    <t>Logged in and on the /inventory-vendors dashboard; the left sidebar nav (Dashboard, Inventory, Quick Inventory, Vendors, Orders, …) is visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in with the provided credentials
+2. Click the 'Main Location' button
+3. Wait for the dashboard sidebar to finish loading
+4. Click the 'Inventory' tab in the left sidebar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: Inventory
+Dashboard URL: https://moontower.aiimone.com/inventory-vendors</t>
+  </si>
+  <si>
+    <t>Inventory view is active: the 'Inventory' heading is visible, the URL stays https://moontower.aiimone.com/inventory-vendors, and the Inventory tab is highlighted (active styling)</t>
+  </si>
+  <si>
+    <t>User is working in the Inventory section of the dashboard</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1084,12 +1166,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF155724"/>
-      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1110,7 +1186,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,11 +1196,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A8FB8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1170,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1182,12 +1253,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1529,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1589,7 +1657,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1630,42 +1698,106 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5">
-        <v>48</v>
-      </c>
-      <c r="D4" s="5">
-        <v>28</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="5">
-        <v>15</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="4">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="5">
+      <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>19</v>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1693,63 +1825,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1757,31 +1889,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -1789,31 +1921,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -1830,7 +1962,7 @@
         <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>57</v>
@@ -1845,7 +1977,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -1853,22 +1985,22 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>59</v>
@@ -1877,7 +2009,7 @@
         <v>60</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -1885,22 +2017,22 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>59</v>
@@ -1909,7 +2041,7 @@
         <v>60</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -1917,31 +2049,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -1949,31 +2081,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -1981,31 +2113,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2013,31 +2145,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2045,31 +2177,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2077,63 +2209,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2141,31 +2273,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2173,31 +2305,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2205,127 +2337,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2333,97 +2465,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2452,866 +2584,1200 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>4</v>
+      <c r="E3" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="361">
   <si>
     <t>FEATURE</t>
   </si>
@@ -53,16 +53,22 @@
     <t>Login</t>
   </si>
   <si>
+    <t>2026-07-01 12:14:01</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>user-signup</t>
+  </si>
+  <si>
+    <t>SignUp-001</t>
+  </si>
+  <si>
     <t>never</t>
   </si>
   <si>
     <t>NOT RUN</t>
-  </si>
-  <si>
-    <t>user-signup</t>
-  </si>
-  <si>
-    <t>SignUp-001</t>
   </si>
   <si>
     <t>verify-dashboard</t>
@@ -141,7 +147,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
+    <t>Passed in 5.0s on webkit.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -171,6 +177,9 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
+    <t>Passed in 4.3s on webkit.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -189,6 +198,9 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
+    <t>Passed in 3.4s on webkit.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -213,6 +225,9 @@
     <t>User remains on /Login</t>
   </si>
   <si>
+    <t>Passed in 12.4s on webkit.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -268,6 +283,9 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
+    <t>Passed in 13.8s on webkit.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -285,6 +303,9 @@
 Password: Whatever!2025</t>
   </si>
   <si>
+    <t>Passed in 12.3s on webkit.</t>
+  </si>
+  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -301,6 +322,9 @@
   </si>
   <si>
     <t>Password input has attribute type='password'</t>
+  </si>
+  <si>
+    <t>Passed in 2.3s on webkit.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -323,6 +347,9 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
+    <t>Passed in 3.9s on webkit.</t>
+  </si>
+  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -342,6 +369,9 @@
     <t>User signed in</t>
   </si>
   <si>
+    <t>Passed in 3.7s on webkit.</t>
+  </si>
+  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -378,6 +408,9 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
+    <t>Passed in 2.6s on webkit.</t>
+  </si>
+  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -393,6 +426,9 @@
     <t>User on the signup screen</t>
   </si>
   <si>
+    <t>Passed in 2.7s on webkit.</t>
+  </si>
+  <si>
     <t>Login-NAV-03</t>
   </si>
   <si>
@@ -406,6 +442,9 @@
   </si>
   <si>
     <t>User on homepage</t>
+  </si>
+  <si>
+    <t>Passed in 2.5s on webkit.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -559,6 +598,9 @@
   </si>
   <si>
     <t>New tenant created</t>
+  </si>
+  <si>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>SignUp-001-AC2-POS-01</t>
@@ -1150,7 +1192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1166,6 +1208,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF155724"/>
+      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1186,7 +1234,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1196,6 +1244,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A8FB8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1241,7 +1294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1253,9 +1306,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1657,7 +1713,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1698,18 +1754,18 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -1730,18 +1786,18 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
@@ -1762,42 +1818,42 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5">
+        <v>55</v>
+      </c>
+      <c r="D6" s="5">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4">
-        <v>35</v>
-      </c>
-      <c r="E6" s="4">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
+        <v>15</v>
+      </c>
+      <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>21</v>
+      <c r="I6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1825,63 +1881,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1889,31 +1945,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -1921,31 +1977,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -1953,31 +2009,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -1985,31 +2041,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2017,31 +2073,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2049,31 +2105,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2081,31 +2137,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2113,31 +2169,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2145,31 +2201,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2177,31 +2233,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2209,63 +2265,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2273,31 +2329,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2305,31 +2361,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2337,127 +2393,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J18" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2465,97 +2521,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2584,865 +2640,865 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J27" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3471,130 +3527,130 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3622,162 +3678,162 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="372">
   <si>
     <t>FEATURE</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-07-01 12:14:01</t>
+    <t>2026-07-01 16:40:20</t>
   </si>
   <si>
     <t>PASS</t>
@@ -63,12 +63,6 @@
   </si>
   <si>
     <t>SignUp-001</t>
-  </si>
-  <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
   </si>
   <si>
     <t>verify-dashboard</t>
@@ -147,7 +141,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 5.0s on webkit.</t>
+    <t>Passed in 16.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -177,7 +171,7 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 4.3s on webkit.</t>
+    <t>Passed in 14.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -198,7 +192,7 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Passed in 3.4s on webkit.</t>
+    <t>Passed in 17.8s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -225,7 +219,7 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 12.4s on webkit.</t>
+    <t>Passed in 31.2s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -246,6 +240,9 @@
 Password: (empty)</t>
   </si>
   <si>
+    <t>Passed in 29.0s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -263,6 +260,9 @@
 Password: (empty)</t>
   </si>
   <si>
+    <t>Passed in 26.6s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
@@ -283,7 +283,7 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
-    <t>Passed in 13.8s on webkit.</t>
+    <t>Passed in 28.4s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -303,7 +303,7 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 12.3s on webkit.</t>
+    <t>Passed in 29.7s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-01</t>
@@ -324,7 +324,7 @@
     <t>Password input has attribute type='password'</t>
   </si>
   <si>
-    <t>Passed in 2.3s on webkit.</t>
+    <t>Passed in 2.0s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -347,7 +347,7 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
-    <t>Passed in 3.9s on webkit.</t>
+    <t>Passed in 2.1s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-03</t>
@@ -369,7 +369,7 @@
     <t>User signed in</t>
   </si>
   <si>
-    <t>Passed in 3.7s on webkit.</t>
+    <t>Passed in 4.7s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-04</t>
@@ -408,7 +408,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 2.6s on webkit.</t>
+    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -426,7 +426,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 2.7s on webkit.</t>
+    <t>Passed in 2.6s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -444,7 +444,7 @@
     <t>User on homepage</t>
   </si>
   <si>
-    <t>Passed in 2.5s on webkit.</t>
+    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -603,6 +603,9 @@
     <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
+    <t>NOT RUN</t>
+  </si>
+  <si>
     <t>SignUp-001-AC2-POS-01</t>
   </si>
   <si>
@@ -689,6 +692,9 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
+    <t>Passed in 3.0s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
@@ -771,6 +777,9 @@
   </si>
   <si>
     <t>Subdomain ∈ /^[a-z0-9-]+$/; contains 'my' + 'eatery'</t>
+  </si>
+  <si>
+    <t>Passed in 2.7s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -858,6 +867,9 @@
     <t>All three have the readonly attribute</t>
   </si>
   <si>
+    <t>Passed in 4.1s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-UI-02</t>
   </si>
   <si>
@@ -932,7 +944,13 @@
     <t>User on the login screen</t>
   </si>
   <si>
+    <t>Passed in 4.0s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NAV-02</t>
+  </si>
+  <si>
+    <t>Passed in 3.7s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -1099,6 +1117,9 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
+    <t>Passed in 3.2s on chromium.</t>
+  </si>
+  <si>
     <t>Dashboard-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1148,10 +1169,19 @@
     <t>User is on the inventory-vendors dashboard</t>
   </si>
   <si>
+    <t>Passed in 4.4s on chromium.</t>
+  </si>
+  <si>
     <t>DashBoard-002-AC1-POS-01</t>
   </si>
   <si>
+    <t>Passed in 3.3s on chromium.</t>
+  </si>
+  <si>
     <t>DashBoard-002-AC2-POS-01</t>
+  </si>
+  <si>
+    <t>Passed in 4.3s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC3-POS-01</t>
@@ -1186,6 +1216,9 @@
   </si>
   <si>
     <t>User is working in the Inventory section of the dashboard</t>
+  </si>
+  <si>
+    <t>Passed in 4.6s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -1218,18 +1251,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF856404"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF4338CA"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF856404"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -1253,17 +1286,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -1306,10 +1339,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1745,7 +1778,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -1754,18 +1787,18 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -1777,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1786,18 +1819,18 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
@@ -1809,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1818,42 +1851,42 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="4">
         <v>55</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>35</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>20</v>
       </c>
-      <c r="F6" s="5">
-        <v>15</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6" s="4">
+        <v>33</v>
+      </c>
+      <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>23</v>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1881,63 +1914,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1945,31 +1978,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -1977,31 +2010,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2009,31 +2042,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -2041,31 +2074,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2073,31 +2106,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2114,7 +2147,7 @@
         <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>79</v>
@@ -2126,7 +2159,7 @@
         <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>82</v>
@@ -2146,7 +2179,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>86</v>
@@ -2158,7 +2191,7 @@
         <v>81</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>88</v>
@@ -2178,7 +2211,7 @@
         <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>92</v>
@@ -2248,7 +2281,7 @@
         <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>107</v>
@@ -2274,7 +2307,7 @@
         <v>112</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>113</v>
@@ -2291,7 +2324,7 @@
       <c r="I13" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2306,7 +2339,7 @@
         <v>118</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>119</v>
@@ -2338,7 +2371,7 @@
         <v>124</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>125</v>
@@ -2370,7 +2403,7 @@
         <v>130</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>131</v>
@@ -2402,7 +2435,7 @@
         <v>137</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>138</v>
@@ -2419,7 +2452,7 @@
       <c r="I17" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2434,7 +2467,7 @@
         <v>142</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>143</v>
@@ -2451,7 +2484,7 @@
       <c r="I18" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2466,7 +2499,7 @@
         <v>147</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>148</v>
@@ -2478,12 +2511,12 @@
         <v>150</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2498,7 +2531,7 @@
         <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>154</v>
@@ -2530,13 +2563,13 @@
         <v>157</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>159</v>
@@ -2547,7 +2580,7 @@
       <c r="I21" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2562,7 +2595,7 @@
         <v>162</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>163</v>
@@ -2574,12 +2607,12 @@
         <v>165</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2594,7 +2627,7 @@
         <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>168</v>
@@ -2611,7 +2644,7 @@
       <c r="I23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2640,34 +2673,34 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2698,415 +2731,415 @@
       <c r="I2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+      <c r="J2" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+      <c r="J3" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
+        <v>208</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>102</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>17</v>
+        <v>235</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>17</v>
+        <v>128</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>17</v>
+        <v>128</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>17</v>
+        <v>262</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>93</v>
@@ -3114,25 +3147,25 @@
       <c r="I15" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>100</v>
@@ -3144,88 +3177,88 @@
         <v>93</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>17</v>
+        <v>208</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>17</v>
+        <v>286</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>131</v>
@@ -3240,33 +3273,33 @@
         <v>133</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
+        <v>288</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>93</v>
@@ -3274,31 +3307,31 @@
       <c r="I20" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>93</v>
@@ -3306,31 +3339,31 @@
       <c r="I21" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>93</v>
@@ -3338,95 +3371,95 @@
       <c r="I22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>17</v>
+        <v>208</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>93</v>
@@ -3434,31 +3467,31 @@
       <c r="I25" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>93</v>
@@ -3466,39 +3499,39 @@
       <c r="I26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3527,130 +3560,130 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>340</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>262</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>356</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3678,162 +3711,162 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>358</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>360</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>288</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>17</v>
+        <v>371</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -6,16 +6,17 @@
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Login" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="SignUp-001" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Dashboard-001" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="DashBoard-002" state="visible" r:id="rId8"/>
+    <sheet sheetId="3" name="Order-01" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="SignUp-001" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Dashboard-001" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="DashBoard-002" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="360">
   <si>
     <t>FEATURE</t>
   </si>
@@ -53,10 +54,22 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-07-01 16:40:20</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
+  </si>
+  <si>
+    <t>order-flow</t>
+  </si>
+  <si>
+    <t>Order-01</t>
+  </si>
+  <si>
+    <t>2026-07-16 18:15:17</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -141,7 +154,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 16.9s on chromium.</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -171,9 +184,6 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 14.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -192,9 +202,6 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Passed in 17.8s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -219,9 +226,6 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 31.2s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -240,9 +244,6 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 29.0s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -260,9 +261,6 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 26.6s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
@@ -283,9 +281,6 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
-    <t>Passed in 28.4s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -303,9 +298,6 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 29.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -322,9 +314,6 @@
   </si>
   <si>
     <t>Password input has attribute type='password'</t>
-  </si>
-  <si>
-    <t>Passed in 2.0s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -347,9 +336,6 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
-    <t>Passed in 2.1s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -369,9 +355,6 @@
     <t>User signed in</t>
   </si>
   <si>
-    <t>Passed in 4.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -408,9 +391,6 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 2.9s on chromium.</t>
-  </si>
-  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -426,9 +406,6 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 2.6s on chromium.</t>
-  </si>
-  <si>
     <t>Login-NAV-03</t>
   </si>
   <si>
@@ -442,9 +419,6 @@
   </si>
   <si>
     <t>User on homepage</t>
-  </si>
-  <si>
-    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -569,6 +543,50 @@
   </si>
   <si>
     <t>Account throttled or locked</t>
+  </si>
+  <si>
+    <t>Order-01-ORDER-01</t>
+  </si>
+  <si>
+    <t>Order-01: Send all vendor orders from the tablet POS and review a sent order</t>
+  </si>
+  <si>
+    <t>Log in, build orders in the tablet POS, send all vendor orders, then review an order in the Orders List</t>
+  </si>
+  <si>
+    <t>Browser open at /login; account 'testing@yopmail.com' exists; tablet POS ordering available for Main Location; vendors have items with PAR levels so an order can be built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to https://moontower.aiimone.com/login
+2. Sign in with testing@yopmail.com / 12345678
+3. Confirm redirect to the location-picker (/select-location)
+4. Select the 'Main Location' location (→ /inventory-vendors)
+5. Click 'Quick Inventory' then 'Inventory' in the sidebar
+6. Enable tablet view (Tablet Preview toggle → 'Exit tablet' appears)
+7. Open the tablet 'Orders' tab
+8. Click 'Continue to Vendors → (N)'
+9. Click 'Review All Orders →' (heading 'Review order before sending')
+10. Click 'Send N orders' (DESTRUCTIVE — submits real vendor orders)
+11. Verify each vendor row shows 'Sent ✓' (real confirmation)
+12. Toggle the 'GORDON' vendor (opens its editor) and click 'Cancel'
+13. Exit tablet view
+14. Open sidebar 'Orders' → 'Orders List' (/order-history)
+15. View order number 2 and inspect its details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: testing@yopmail.com
+Password: 12345678
+Expected confirmation: 5 vendors show 'Sent ✓'
+Product sought in order details: Sprite</t>
+  </si>
+  <si>
+    <t>Orders are submitted (5 vendors → 'Sent ✓'); the Orders List shows the new Submitted orders; the opened order's details list its product lines</t>
+  </si>
+  <si>
+    <t>5 new 'Submitted' vendor orders exist in /order-history</t>
+  </si>
+  <si>
+    <t>Failed in 44.9s: Error: AC (order details): expected "Sprite" in the opened order details (order opened = "PFG — 07/16/2026"). Note: exploration found "Sprite" in the SYSCO order; a freshly-sent batch's list order is non-deterministic, so "order number 2" is not a stable reference to the Sprite-containing order.</t>
   </si>
   <si>
     <t>SignUp-001-AC1-POS-01</t>
@@ -600,12 +618,6 @@
     <t>New tenant created</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
-  </si>
-  <si>
     <t>SignUp-001-AC2-POS-01</t>
   </si>
   <si>
@@ -692,9 +704,6 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
@@ -777,9 +786,6 @@
   </si>
   <si>
     <t>Subdomain ∈ /^[a-z0-9-]+$/; contains 'my' + 'eatery'</t>
-  </si>
-  <si>
-    <t>Passed in 2.7s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -867,9 +873,6 @@
     <t>All three have the readonly attribute</t>
   </si>
   <si>
-    <t>Passed in 4.1s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-UI-02</t>
   </si>
   <si>
@@ -944,13 +947,7 @@
     <t>User on the login screen</t>
   </si>
   <si>
-    <t>Passed in 4.0s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NAV-02</t>
-  </si>
-  <si>
-    <t>Passed in 3.7s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -1117,9 +1114,6 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
-    <t>Passed in 3.2s on chromium.</t>
-  </si>
-  <si>
     <t>Dashboard-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1169,19 +1163,10 @@
     <t>User is on the inventory-vendors dashboard</t>
   </si>
   <si>
-    <t>Passed in 4.4s on chromium.</t>
-  </si>
-  <si>
     <t>DashBoard-002-AC1-POS-01</t>
   </si>
   <si>
-    <t>Passed in 3.3s on chromium.</t>
-  </si>
-  <si>
     <t>DashBoard-002-AC2-POS-01</t>
-  </si>
-  <si>
-    <t>Passed in 4.3s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC3-POS-01</t>
@@ -1216,9 +1201,6 @@
   </si>
   <si>
     <t>User is working in the Inventory section of the dashboard</t>
-  </si>
-  <si>
-    <t>Passed in 4.6s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1227,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF155724"/>
+      <color rgb="FF856404"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF721C24"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -1257,12 +1245,6 @@
     <font>
       <b/>
       <color rgb="FF4338CA"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF856404"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -1281,7 +1263,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1292,11 +1279,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -1339,10 +1321,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1686,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1746,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1769,48 +1751,48 @@
         <v>15</v>
       </c>
       <c r="C3" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2">
         <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1827,22 +1809,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1858,35 +1840,67 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5">
+        <v>56</v>
+      </c>
+      <c r="D7" s="5">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4">
-        <v>35</v>
-      </c>
-      <c r="E6" s="4">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
-        <v>33</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="F7" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="4">
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>21</v>
+      <c r="I7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1914,63 +1928,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1978,31 +1992,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2010,31 +2024,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2042,31 +2056,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -2074,31 +2088,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2115,7 +2129,7 @@
         <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>73</v>
@@ -2124,13 +2138,13 @@
         <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2138,31 +2152,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2170,31 +2184,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2202,31 +2216,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2234,31 +2248,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2266,31 +2280,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2298,63 +2312,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2362,31 +2376,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2394,31 +2408,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2426,127 +2440,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2554,97 +2568,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2655,6 +2669,93 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" ht="240" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -2673,34 +2774,34 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2729,71 +2830,71 @@
         <v>179</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>181</v>
+        <v>44</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>181</v>
+        <v>44</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2801,63 +2902,63 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>208</v>
+        <v>44</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2865,31 +2966,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2897,95 +2998,95 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>235</v>
+        <v>44</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2993,31 +3094,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -3025,63 +3126,63 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -3089,31 +3190,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>262</v>
+        <v>44</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -3121,63 +3222,63 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>208</v>
+        <v>44</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -3185,63 +3286,63 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>285</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>286</v>
+        <v>44</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3249,31 +3350,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>288</v>
+        <v>44</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3281,159 +3382,159 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>208</v>
+        <v>44</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3441,97 +3542,97 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J26" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3541,7 +3642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -3560,63 +3661,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>340</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3624,31 +3725,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>262</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3656,31 +3757,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>356</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3692,7 +3793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -3711,63 +3812,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>358</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3775,31 +3876,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>360</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3807,31 +3908,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>288</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3839,31 +3940,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>371</v>
+        <v>44</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases.xlsx
+++ b/reports/Test-Cases.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="357">
   <si>
     <t>FEATURE</t>
   </si>
@@ -64,12 +64,6 @@
   </si>
   <si>
     <t>Order-01</t>
-  </si>
-  <si>
-    <t>2026-07-16 18:15:17</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -586,9 +580,6 @@
     <t>5 new 'Submitted' vendor orders exist in /order-history</t>
   </si>
   <si>
-    <t>Failed in 44.9s: Error: AC (order details): expected "Sprite" in the opened order details (order opened = "PFG — 07/16/2026"). Note: exploration found "Sprite" in the SYSCO order; a freshly-sent batch's list order is non-deterministic, so "order number 2" is not a stable reference to the Sprite-containing order.</t>
-  </si>
-  <si>
     <t>SignUp-001-AC1-POS-01</t>
   </si>
   <si>
@@ -1207,7 +1198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1233,12 +1224,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF721C24"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1249,7 +1234,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1264,11 +1249,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1309,7 +1289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1321,12 +1301,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1763,24 +1740,24 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>26</v>
@@ -1809,10 +1786,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -1841,10 +1818,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -1872,35 +1849,35 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4">
         <v>56</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>36</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>20</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>25</v>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1928,63 +1905,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1992,31 +1969,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2024,31 +2001,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2056,31 +2033,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -2088,31 +2065,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2120,31 +2097,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2152,31 +2129,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2184,31 +2161,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2216,31 +2193,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2248,31 +2225,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2280,31 +2257,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2312,63 +2289,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2376,31 +2353,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2408,31 +2385,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2440,127 +2417,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2568,97 +2545,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2687,66 +2664,66 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="240" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2774,63 +2751,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -2838,31 +2815,31 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2870,31 +2847,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2902,63 +2879,63 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2966,31 +2943,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2998,95 +2975,95 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -3094,31 +3071,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -3126,63 +3103,63 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -3190,31 +3167,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -3222,63 +3199,63 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -3286,63 +3263,63 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3350,31 +3327,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3382,159 +3359,159 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3542,97 +3519,97 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3661,63 +3638,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3725,31 +3702,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3757,31 +3734,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3812,63 +3789,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3876,31 +3853,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3908,31 +3885,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3940,31 +3917,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
